--- a/files/港岛-香港仔及鸭脷洲-PORTO.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-PORTO.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porto 销控表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -111,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -176,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -192,51 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -680,7 +541,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -730,7 +591,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -780,7 +641,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -830,7 +691,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -880,7 +741,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -930,7 +791,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -980,7 +841,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -1026,7 +887,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1072,7 +933,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -1122,7 +983,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1168,7 +1029,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -1218,7 +1079,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1268,7 +1129,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1318,7 +1179,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1364,7 +1225,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1410,7 +1271,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1460,7 +1321,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1506,7 +1367,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1556,7 +1417,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1606,7 +1467,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1656,7 +1517,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1702,7 +1563,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1748,7 +1609,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1798,7 +1659,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1844,7 +1705,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1890,7 +1751,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1940,7 +1801,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1990,7 +1851,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -2036,7 +1897,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -2082,7 +1943,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -2128,7 +1989,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -2156,7 +2017,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2174,7 +2035,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -2220,7 +2081,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -2270,7 +2131,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -2320,7 +2181,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -2366,7 +2227,7 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -2412,7 +2273,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -2458,7 +2319,7 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -2504,7 +2365,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -2550,7 +2411,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -2600,7 +2461,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -2650,7 +2511,7 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -2696,7 +2557,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -2742,7 +2603,7 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -2788,7 +2649,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -2834,7 +2695,7 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -2880,7 +2741,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -2930,7 +2791,7 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -2976,7 +2837,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -3022,7 +2883,7 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -3068,7 +2929,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -3114,7 +2975,7 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -3142,7 +3003,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -3160,7 +3021,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -3206,7 +3067,7 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -3256,7 +3117,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -3302,7 +3163,7 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -3330,7 +3191,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -3348,7 +3209,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -3394,7 +3255,7 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -3440,7 +3301,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -3486,7 +3347,7 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -3514,7 +3375,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -3532,7 +3393,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -3578,7 +3439,7 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -3624,7 +3485,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -3652,7 +3513,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -3670,7 +3531,7 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -3716,7 +3577,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -3762,7 +3623,7 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -3790,7 +3651,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -3808,7 +3669,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -3854,7 +3715,7 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -3900,7 +3761,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -3946,7 +3807,7 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -3974,7 +3835,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -3992,7 +3853,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -4038,7 +3899,7 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -4084,7 +3945,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -4112,7 +3973,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -4130,7 +3991,7 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -4158,7 +4019,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -4176,7 +4037,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -4222,7 +4083,7 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -4268,7 +4129,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -4296,7 +4157,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -4314,7 +4175,7 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -4342,7 +4203,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -4360,7 +4221,7 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -4388,7 +4249,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -4406,7 +4267,7 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -4434,7 +4295,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -4452,7 +4313,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -4480,7 +4341,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -4498,7 +4359,7 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -4544,7 +4405,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -4590,7 +4451,7 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -4618,7 +4479,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -4636,7 +4497,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -4682,7 +4543,7 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -4728,7 +4589,7 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -4756,7 +4617,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -4774,7 +4635,7 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -4820,7 +4681,7 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -4866,7 +4727,7 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -4912,7 +4773,7 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -4940,7 +4801,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -4958,7 +4819,7 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -5004,7 +4865,7 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -5032,7 +4893,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -5050,7 +4911,7 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -5078,7 +4939,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -5096,7 +4957,7 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -5124,7 +4985,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -5142,7 +5003,7 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -5188,7 +5049,7 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -5238,7 +5099,7 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -5288,7 +5149,7 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -5334,7 +5195,7 @@
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -5362,7 +5223,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -5380,7 +5241,7 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -5408,7 +5269,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -5426,7 +5287,7 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -5472,7 +5333,7 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -5518,7 +5379,7 @@
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -5564,7 +5425,7 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -5592,7 +5453,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -5610,7 +5471,7 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -5638,7 +5499,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -5656,7 +5517,7 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -5684,7 +5545,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -5702,7 +5563,7 @@
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -5748,7 +5609,7 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -5794,7 +5655,7 @@
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -5822,7 +5683,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -5840,7 +5701,7 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -5868,7 +5729,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -5886,7 +5747,7 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -5932,7 +5793,7 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -5978,7 +5839,7 @@
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -6006,7 +5867,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -6024,7 +5885,7 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -6052,7 +5913,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -6070,7 +5931,7 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -6098,7 +5959,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -6116,7 +5977,7 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -6144,7 +6005,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -6162,7 +6023,7 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -6190,7 +6051,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -6208,7 +6069,7 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -6236,7 +6097,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -6254,7 +6115,7 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -6282,7 +6143,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -6300,7 +6161,7 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
@@ -6346,7 +6207,7 @@
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -6392,7 +6253,7 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
@@ -6420,7 +6281,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -6438,7 +6299,7 @@
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -6466,7 +6327,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -6484,7 +6345,7 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
@@ -6512,7 +6373,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -6530,7 +6391,7 @@
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -6558,7 +6419,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -6576,7 +6437,7 @@
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
@@ -6622,7 +6483,7 @@
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -6650,7 +6511,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -6668,7 +6529,7 @@
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
@@ -6696,7 +6557,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -6714,7 +6575,7 @@
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -6760,7 +6621,7 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
@@ -6806,7 +6667,7 @@
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -6834,7 +6695,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -6852,7 +6713,7 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
@@ -6880,7 +6741,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -6898,7 +6759,7 @@
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -6926,7 +6787,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -6944,7 +6805,7 @@
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
@@ -6972,7 +6833,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -6990,7 +6851,7 @@
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -7018,7 +6879,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -7036,7 +6897,7 @@
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
@@ -7064,7 +6925,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -7082,7 +6943,7 @@
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -7110,7 +6971,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -7128,7 +6989,7 @@
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
@@ -7174,7 +7035,7 @@
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -7220,7 +7081,7 @@
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
@@ -7248,7 +7109,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -7266,7 +7127,7 @@
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -7294,7 +7155,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -7312,7 +7173,7 @@
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -7358,7 +7219,7 @@
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -7386,7 +7247,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -7404,7 +7265,7 @@
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
@@ -7450,7 +7311,7 @@
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -7478,7 +7339,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -7496,7 +7357,7 @@
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
@@ -7542,7 +7403,7 @@
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -7588,7 +7449,7 @@
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
@@ -7634,7 +7495,7 @@
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -7662,7 +7523,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -7680,7 +7541,7 @@
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
@@ -7708,7 +7569,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -7726,7 +7587,7 @@
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
@@ -7754,7 +7615,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -7772,7 +7633,7 @@
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
@@ -7800,7 +7661,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -7818,7 +7679,7 @@
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -7864,7 +7725,7 @@
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
@@ -7892,7 +7753,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -7910,7 +7771,7 @@
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -7938,7 +7799,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -7956,7 +7817,7 @@
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
@@ -8002,7 +7863,7 @@
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -8048,7 +7909,7 @@
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
@@ -8076,7 +7937,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -8094,7 +7955,7 @@
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -8122,7 +7983,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -8140,7 +8001,7 @@
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
@@ -8186,7 +8047,7 @@
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -8214,7 +8075,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -8232,7 +8093,7 @@
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
@@ -8278,7 +8139,7 @@
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -8306,7 +8167,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -8324,7 +8185,7 @@
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
@@ -8370,7 +8231,7 @@
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -8420,7 +8281,7 @@
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
@@ -8470,7 +8331,7 @@
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -8520,7 +8381,7 @@
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
@@ -8570,7 +8431,7 @@
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -8620,7 +8481,7 @@
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -8670,7 +8531,7 @@
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -8720,7 +8581,7 @@
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
@@ -8770,7 +8631,7 @@
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PORTO</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -8824,1759 +8685,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:J29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>PORTO - Porto 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>174 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>44 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>32 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>64 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>34 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>28&amp;29/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 757呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 746呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr"/>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>D | 644呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F6" s="17" t="inlineStr"/>
-      <c r="G6" s="17" t="inlineStr"/>
-      <c r="H6" s="17" t="inlineStr"/>
-      <c r="I6" s="17" t="inlineStr"/>
-      <c r="J6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr"/>
-      <c r="C7" s="17" t="inlineStr"/>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>C | 286呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr"/>
-      <c r="F7" s="17" t="inlineStr"/>
-      <c r="G7" s="17" t="inlineStr"/>
-      <c r="H7" s="17" t="inlineStr"/>
-      <c r="I7" s="17" t="inlineStr"/>
-      <c r="J7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 388呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>B | 241呎 (1房)
-$895万
-$37,120/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>C | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>D | 270呎 (1房)
-$846万
-$31,337/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F8" s="18" t="inlineStr">
-        <is>
-          <t>E | 255呎 (1房)
-$837万
-$32,820/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
-        <is>
-          <t>F | 384呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H8" s="16" t="inlineStr">
-        <is>
-          <t>G | 219呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I8" s="17" t="inlineStr"/>
-      <c r="J8" s="17" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 388呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="19" t="inlineStr">
-        <is>
-          <t>B | 241呎 (1房)
-$884万
-$36,668/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>C | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>D | 270呎 (1房)
-$839万
-$31,089/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F9" s="19" t="inlineStr">
-        <is>
-          <t>E | 255呎 (1房)
-$827万
-$32,443/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>F | 384呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H9" s="16" t="inlineStr">
-        <is>
-          <t>G | 219呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I9" s="17" t="inlineStr"/>
-      <c r="J9" s="17" t="inlineStr"/>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>A | 388呎 (2房)
-$1,338万
-$34,490/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>B | 241呎 (1房)
-$873万
-$36,220/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>C | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>D | 270呎 (1房)
-$833万
-$30,841/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F10" s="18" t="inlineStr">
-        <is>
-          <t>E | 255呎 (1房)
-$818万
-$32,071/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="inlineStr">
-        <is>
-          <t>F | 384呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H10" s="16" t="inlineStr">
-        <is>
-          <t>G | 219呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I10" s="17" t="inlineStr"/>
-      <c r="J10" s="17" t="inlineStr"/>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>A | 388呎 (2房)
-$1,319万
-$33,995/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C11" s="20" t="inlineStr">
-        <is>
-          <t>B | 241呎 (1房)
-$720万
-$29,871/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D11" s="19" t="inlineStr">
-        <is>
-          <t>C | 436呎 (2房)
-$1,493万
-$34,245/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>D | 270呎 (1房)
-$826万
-$30,593/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F11" s="19" t="inlineStr">
-        <is>
-          <t>E | 255呎 (1房)
-$808万
-$31,702/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G11" s="16" t="inlineStr">
-        <is>
-          <t>F | 384呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H11" s="16" t="inlineStr">
-        <is>
-          <t>G | 219呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I11" s="17" t="inlineStr"/>
-      <c r="J11" s="17" t="inlineStr"/>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 388呎 (2房)
-$1,300万
-$33,500/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C12" s="19" t="inlineStr">
-        <is>
-          <t>B | 241呎 (1房)
-$851万
-$35,324/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>C | 436呎 (2房)
-$1,466万
-$33,624/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E12" s="18" t="inlineStr">
-        <is>
-          <t>D | 270呎 (1房)
-$819万
-$30,344/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F12" s="18" t="inlineStr">
-        <is>
-          <t>E | 255呎 (1房)
-$802万
-$31,451/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G12" s="16" t="inlineStr">
-        <is>
-          <t>F | 384呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H12" s="16" t="inlineStr">
-        <is>
-          <t>G | 219呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I12" s="17" t="inlineStr"/>
-      <c r="J12" s="17" t="inlineStr"/>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>A | 388呎 (2房)
-$1,281万
-$33,005/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>B | 241呎 (1房)
-$840万
-$34,876/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>C | 436呎 (2房)
-$1,439万
-$33,005/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E13" s="19" t="inlineStr">
-        <is>
-          <t>D | 270呎 (1房)
-$812万
-$30,093/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F13" s="18" t="inlineStr">
-        <is>
-          <t>E | 255呎 (1房)
-$796万
-$31,204/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G13" s="16" t="inlineStr">
-        <is>
-          <t>F | 384呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H13" s="16" t="inlineStr">
-        <is>
-          <t>G | 219呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I13" s="17" t="inlineStr"/>
-      <c r="J13" s="17" t="inlineStr"/>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>A | 388呎 (2房)
-$1,261万
-$32,508/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C14" s="20" t="inlineStr">
-        <is>
-          <t>B | 241呎 (1房)
-$693万
-$28,743/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>C | 436呎 (2房)
-$1,412万
-$32,385/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E14" s="19" t="inlineStr">
-        <is>
-          <t>D | 270呎 (1房)
-$806万
-$29,844/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F14" s="19" t="inlineStr">
-        <is>
-          <t>E | 255呎 (1房)
-$789万
-$30,953/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G14" s="19" t="inlineStr">
-        <is>
-          <t>F | 384呎 (2房)
-$1,268万
-$33,018/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H14" s="16" t="inlineStr">
-        <is>
-          <t>G | 219呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I14" s="17" t="inlineStr"/>
-      <c r="J14" s="17" t="inlineStr"/>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B15" s="20" t="inlineStr">
-        <is>
-          <t>A | 388呎 (2房)
-$1,037万
-$26,727/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="19" t="inlineStr">
-        <is>
-          <t>B | 241呎 (1房)
-$819万
-$33,975/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>C | 436呎 (2房)
-$1,385万
-$31,764/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E15" s="19" t="inlineStr">
-        <is>
-          <t>D | 270呎 (1房)
-$799万
-$29,596/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F15" s="20" t="inlineStr">
-        <is>
-          <t>E | 255呎 (1房)
-$648万
-$25,412/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G15" s="18" t="inlineStr">
-        <is>
-          <t>F | 384呎 (2房)
-$1,249万
-$32,526/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H15" s="16" t="inlineStr">
-        <is>
-          <t>G | 219呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I15" s="17" t="inlineStr"/>
-      <c r="J15" s="17" t="inlineStr"/>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B16" s="19" t="inlineStr">
-        <is>
-          <t>A | 388呎 (2房)
-$1,224万
-$31,552/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C16" s="20" t="inlineStr">
-        <is>
-          <t>B | 241呎 (1房)
-$675万
-$27,996/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D16" s="19" t="inlineStr">
-        <is>
-          <t>C | 436呎 (2房)
-$1,365万
-$31,303/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E16" s="19" t="inlineStr">
-        <is>
-          <t>D | 270呎 (1房)
-$792万
-$29,348/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F16" s="20" t="inlineStr">
-        <is>
-          <t>E | 255呎 (1房)
-$626万
-$24,549/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G16" s="18" t="inlineStr">
-        <is>
-          <t>F | 384呎 (2房)
-$1,230万
-$32,026/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H16" s="18" t="inlineStr">
-        <is>
-          <t>G | 219呎 (开放式)
-$724万
-$33,050/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I16" s="17" t="inlineStr"/>
-      <c r="J16" s="17" t="inlineStr"/>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B17" s="20" t="inlineStr">
-        <is>
-          <t>A | 388呎 (2房)
-$970万
-$25,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C17" s="20" t="inlineStr">
-        <is>
-          <t>B | 241呎 (1房)
-$653万
-$27,108/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D17" s="20" t="inlineStr">
-        <is>
-          <t>C | 436呎 (2房)
-$1,155万
-$26,495/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E17" s="20" t="inlineStr">
-        <is>
-          <t>D | 270呎 (1房)
-$676万
-$25,026/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F17" s="20" t="inlineStr">
-        <is>
-          <t>E | 255呎 (1房)
-$621万
-$24,349/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G17" s="19" t="inlineStr">
-        <is>
-          <t>F | 384呎 (2房)
-$1,211万
-$31,529/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H17" s="19" t="inlineStr">
-        <is>
-          <t>G | 219呎 (开放式)
-$716万
-$32,680/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="I17" s="17" t="inlineStr"/>
-      <c r="J17" s="17" t="inlineStr"/>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B18" s="20" t="inlineStr">
-        <is>
-          <t>A | 388呎 (2房)
-$954万
-$24,601/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C18" s="20" t="inlineStr">
-        <is>
-          <t>B | 241呎 (1房)
-$652万
-$27,037/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D18" s="20" t="inlineStr">
-        <is>
-          <t>C | 436呎 (2房)
-$1,085万
-$24,894/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E18" s="20" t="inlineStr">
-        <is>
-          <t>D | 270呎 (1房)
-$641万
-$23,733/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F18" s="20" t="inlineStr">
-        <is>
-          <t>E | 255呎 (1房)
-$610万
-$23,922/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G18" s="18" t="inlineStr">
-        <is>
-          <t>F | 384呎 (2房)
-$1,192万
-$31,034/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H18" s="18" t="inlineStr">
-        <is>
-          <t>G | 219呎 (开放式)
-$708万
-$32,306/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I18" s="17" t="inlineStr"/>
-      <c r="J18" s="17" t="inlineStr"/>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B19" s="20" t="inlineStr">
-        <is>
-          <t>A | 388呎 (2房)
-$974万
-$25,103/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C19" s="20" t="inlineStr">
-        <is>
-          <t>B | 241呎 (1房)
-$638万
-$26,490/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D19" s="19" t="inlineStr">
-        <is>
-          <t>C | 436呎 (2房)
-$1,278万
-$29,319/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E19" s="19" t="inlineStr">
-        <is>
-          <t>D | 270呎 (1房)
-$772万
-$28,604/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F19" s="20" t="inlineStr">
-        <is>
-          <t>E | 255呎 (1房)
-$611万
-$23,949/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G19" s="18" t="inlineStr">
-        <is>
-          <t>F | 384呎 (2房)
-$1,173万
-$30,536/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H19" s="18" t="inlineStr">
-        <is>
-          <t>G | 219呎 (开放式)
-$699万
-$31,936/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I19" s="17" t="inlineStr"/>
-      <c r="J19" s="17" t="inlineStr"/>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B20" s="20" t="inlineStr">
-        <is>
-          <t>A | 388呎 (2房)
-$904万
-$23,299/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C20" s="20" t="inlineStr">
-        <is>
-          <t>B | 241呎 (1房)
-$628万
-$26,071/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D20" s="20" t="inlineStr">
-        <is>
-          <t>C | 436呎 (2房)
-$1,016万
-$23,300/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E20" s="19" t="inlineStr">
-        <is>
-          <t>D | 270呎 (1房)
-$766万
-$28,356/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F20" s="20" t="inlineStr">
-        <is>
-          <t>E | 255呎 (1房)
-$606万
-$23,749/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G20" s="19" t="inlineStr">
-        <is>
-          <t>F | 384呎 (2房)
-$1,154万
-$30,039/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H20" s="19" t="inlineStr">
-        <is>
-          <t>G | 219呎 (开放式)
-$691万
-$31,566/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="I20" s="17" t="inlineStr"/>
-      <c r="J20" s="17" t="inlineStr"/>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="inlineStr">
-        <is>
-          <t>A | 388呎 (2房)
-$1,116万
-$28,758/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C21" s="20" t="inlineStr">
-        <is>
-          <t>B | 241呎 (1房)
-$605万
-$25,100/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D21" s="20" t="inlineStr">
-        <is>
-          <t>C | 436呎 (2房)
-$1,038万
-$23,819/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E21" s="19" t="inlineStr">
-        <is>
-          <t>D | 270呎 (1房)
-$756万
-$27,981/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>E | 296呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G21" s="16" t="inlineStr">
-        <is>
-          <t>F | 346呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H21" s="18" t="inlineStr">
-        <is>
-          <t>G | 219呎 (开放式)
-$667万
-$30,470/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I21" s="17" t="inlineStr"/>
-      <c r="J21" s="17" t="inlineStr"/>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B22" s="20" t="inlineStr">
-        <is>
-          <t>A | 389呎 (2房)
-$922万
-$23,715/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C22" s="20" t="inlineStr">
-        <is>
-          <t>B | 241呎 (1房)
-$598万
-$24,801/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D22" s="19" t="inlineStr">
-        <is>
-          <t>C | 438呎 (2房)
-$1,246万
-$28,447/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E22" s="19" t="inlineStr">
-        <is>
-          <t>D | 271呎 (1房)
-$748万
-$27,613/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F22" s="20" t="inlineStr">
-        <is>
-          <t>E | 276呎 (1房)
-$639万
-$23,149/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G22" s="20" t="inlineStr">
-        <is>
-          <t>F | 288呎 (1房)
-$687万
-$23,868/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H22" s="20" t="inlineStr">
-        <is>
-          <t>G | 277呎 (1房)
-$661万
-$23,870/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I22" s="19" t="inlineStr">
-        <is>
-          <t>H | 214呎 (开放式)
-$650万
-$30,369/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="J22" s="18" t="inlineStr">
-        <is>
-          <t>J | 220呎 (开放式)
-$659万
-$29,964/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B23" s="20" t="inlineStr">
-        <is>
-          <t>A | 389呎 (2房)
-$889万
-$22,851/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C23" s="20" t="inlineStr">
-        <is>
-          <t>B | 241呎 (1房)
-$585万
-$24,261/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D23" s="20" t="inlineStr">
-        <is>
-          <t>C | 438呎 (2房)
-$994万
-$22,701/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E23" s="20" t="inlineStr">
-        <is>
-          <t>D | 271呎 (1房)
-$616万
-$22,742/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F23" s="20" t="inlineStr">
-        <is>
-          <t>E | 276呎 (1房)
-$631万
-$22,851/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G23" s="20" t="inlineStr">
-        <is>
-          <t>F | 288呎 (1房)
-$654万
-$22,698/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H23" s="20" t="inlineStr">
-        <is>
-          <t>G | 277呎 (1房)
-$633万
-$22,848/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I23" s="19" t="inlineStr">
-        <is>
-          <t>H | 214呎 (开放式)
-$642万
-$30,000/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="J23" s="18" t="inlineStr">
-        <is>
-          <t>J | 220呎 (开放式)
-$651万
-$29,591/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B24" s="20" t="inlineStr">
-        <is>
-          <t>A | 389呎 (2房)
-$881万
-$22,650/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C24" s="20" t="inlineStr">
-        <is>
-          <t>B | 241呎 (1房)
-$583万
-$24,199/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D24" s="19" t="inlineStr">
-        <is>
-          <t>C | 438呎 (2房)
-$1,227万
-$28,014/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E24" s="20" t="inlineStr">
-        <is>
-          <t>D | 271呎 (1房)
-$604万
-$22,299/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F24" s="20" t="inlineStr">
-        <is>
-          <t>E | 276呎 (1房)
-$640万
-$23,181/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G24" s="20" t="inlineStr">
-        <is>
-          <t>F | 288呎 (1房)
-$646万
-$22,448/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H24" s="20" t="inlineStr">
-        <is>
-          <t>G | 277呎 (1房)
-$644万
-$23,249/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I24" s="19" t="inlineStr">
-        <is>
-          <t>H | 214呎 (开放式)
-$634万
-$29,626/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="J24" s="18" t="inlineStr">
-        <is>
-          <t>J | 220呎 (开放式)
-$643万
-$29,223/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B25" s="20" t="inlineStr">
-        <is>
-          <t>A | 389呎 (2房)
-$873万
-$22,450/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C25" s="20" t="inlineStr">
-        <is>
-          <t>B | 241呎 (1房)
-$576万
-$23,900/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D25" s="20" t="inlineStr">
-        <is>
-          <t>C | 438呎 (2房)
-$981万
-$22,400/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E25" s="20" t="inlineStr">
-        <is>
-          <t>D | 271呎 (1房)
-$572万
-$21,114/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F25" s="20" t="inlineStr">
-        <is>
-          <t>E | 276呎 (1房)
-$608万
-$22,040/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G25" s="20" t="inlineStr">
-        <is>
-          <t>F | 288呎 (1房)
-$665万
-$23,097/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H25" s="20" t="inlineStr">
-        <is>
-          <t>G | 277呎 (1房)
-$616万
-$22,249/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I25" s="19" t="inlineStr">
-        <is>
-          <t>H | 214呎 (开放式)
-$627万
-$29,313/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="J25" s="18" t="inlineStr">
-        <is>
-          <t>J | 220呎 (开放式)
-$636万
-$28,909/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B26" s="19" t="inlineStr">
-        <is>
-          <t>A | 389呎 (2房)
-$1,075万
-$27,640/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C26" s="20" t="inlineStr">
-        <is>
-          <t>B | 241呎 (1房)
-$569万
-$23,602/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D26" s="19" t="inlineStr">
-        <is>
-          <t>C | 438呎 (2房)
-$1,211万
-$27,642/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E26" s="20" t="inlineStr">
-        <is>
-          <t>D | 271呎 (1房)
-$564万
-$20,812/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F26" s="19" t="inlineStr">
-        <is>
-          <t>E | 276呎 (1房)
-$752万
-$27,264/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G26" s="20" t="inlineStr">
-        <is>
-          <t>F | 288呎 (1房)
-$662万
-$22,976/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H26" s="20" t="inlineStr">
-        <is>
-          <t>G | 277呎 (1房)
-$621万
-$22,422/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I26" s="19" t="inlineStr">
-        <is>
-          <t>H | 214呎 (开放式)
-$621万
-$29,005/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="J26" s="19" t="inlineStr">
-        <is>
-          <t>J | 220呎 (开放式)
-$630万
-$28,632/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B27" s="20" t="inlineStr">
-        <is>
-          <t>A | 389呎 (2房)
-$884万
-$22,735/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C27" s="20" t="inlineStr">
-        <is>
-          <t>B | 241呎 (1房)
-$571万
-$23,701/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D27" s="19" t="inlineStr">
-        <is>
-          <t>C | 438呎 (2房)
-$1,202万
-$27,454/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E27" s="20" t="inlineStr">
-        <is>
-          <t>D | 271呎 (1房)
-$573万
-$21,159/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F27" s="20" t="inlineStr">
-        <is>
-          <t>E | 276呎 (1房)
-$614万
-$22,243/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G27" s="20" t="inlineStr">
-        <is>
-          <t>F | 288呎 (1房)
-$631万
-$21,899/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H27" s="20" t="inlineStr">
-        <is>
-          <t>G | 277呎 (1房)
-$618万
-$22,325/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I27" s="19" t="inlineStr">
-        <is>
-          <t>H | 214呎 (开放式)
-$614万
-$28,692/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="J27" s="19" t="inlineStr">
-        <is>
-          <t>J | 220呎 (开放式)
-$623万
-$28,323/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B28" s="19" t="inlineStr">
-        <is>
-          <t>A | 389呎 (2房)
-$1,054万
-$27,105/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C28" s="20" t="inlineStr">
-        <is>
-          <t>B | 241呎 (1房)
-$571万
-$23,705/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D28" s="19" t="inlineStr">
-        <is>
-          <t>C | 438呎 (2房)
-$1,194万
-$27,267/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E28" s="20" t="inlineStr">
-        <is>
-          <t>D | 271呎 (1房)
-$556万
-$20,506/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F28" s="19" t="inlineStr">
-        <is>
-          <t>E | 276呎 (1房)
-$732万
-$26,522/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G28" s="20" t="inlineStr">
-        <is>
-          <t>F | 288呎 (1房)
-$624万
-$21,649/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H28" s="20" t="inlineStr">
-        <is>
-          <t>G | 277呎 (1房)
-$586万
-$21,141/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I28" s="19" t="inlineStr">
-        <is>
-          <t>H | 214呎 (开放式)
-$606万
-$28,304/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="J28" s="19" t="inlineStr">
-        <is>
-          <t>J | 220呎 (开放式)
-$616万
-$28,014/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>A | 350呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>B | 204呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D29" s="16" t="inlineStr">
-        <is>
-          <t>C | 401呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E29" s="16" t="inlineStr">
-        <is>
-          <t>D | 234呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F29" s="16" t="inlineStr">
-        <is>
-          <t>E | 238呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G29" s="16" t="inlineStr">
-        <is>
-          <t>F | 250呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H29" s="16" t="inlineStr">
-        <is>
-          <t>G | 240呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I29" s="16" t="inlineStr">
-        <is>
-          <t>H | 192呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J29" s="16" t="inlineStr">
-        <is>
-          <t>J | 199呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/港岛-香港仔及鸭脷洲-PORTO.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-PORTO.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PORTO" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +42,101 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +147,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +212,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +228,63 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +661,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -8685,4 +8872,1759 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>PORTO 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>C | 286呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr"/>
+      <c r="F5" s="20" t="inlineStr"/>
+      <c r="G5" s="20" t="inlineStr"/>
+      <c r="H5" s="20" t="inlineStr"/>
+      <c r="I5" s="20" t="inlineStr"/>
+      <c r="J5" s="20" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>28&amp;29</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 757呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 746呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 644呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="20" t="inlineStr"/>
+      <c r="H6" s="20" t="inlineStr"/>
+      <c r="I6" s="20" t="inlineStr"/>
+      <c r="J6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 388呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 241呎 (1房)
+$895万
+$37,120/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>C | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>D | 270呎 (1房)
+$846万
+$31,337/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>E | 255呎 (1房)
+$837万
+$32,820/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G7" s="21" t="inlineStr">
+        <is>
+          <t>F | 384呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t>G | 219呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I7" s="20" t="inlineStr"/>
+      <c r="J7" s="20" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 388呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>B | 241呎 (1房)
+$884万
+$36,668/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>C | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>D | 270呎 (1房)
+$839万
+$31,089/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>E | 255呎 (1房)
+$827万
+$32,443/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G8" s="21" t="inlineStr">
+        <is>
+          <t>F | 384呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t>G | 219呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I8" s="20" t="inlineStr"/>
+      <c r="J8" s="20" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 388呎 (2房)
+$1338万
+$34,490/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 241呎 (1房)
+$873万
+$36,220/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>C | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>D | 270呎 (1房)
+$833万
+$30,841/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>E | 255呎 (1房)
+$818万
+$32,071/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G9" s="21" t="inlineStr">
+        <is>
+          <t>F | 384呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>G | 219呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr"/>
+      <c r="J9" s="20" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>A | 388呎 (2房)
+$1319万
+$33,995/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>B | 241呎 (1房)
+$720万
+$29,871/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>C | 436呎 (2房)
+$1493万
+$34,245/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>D | 270呎 (1房)
+$826万
+$30,593/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t>E | 255呎 (1房)
+$808万
+$31,702/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G10" s="21" t="inlineStr">
+        <is>
+          <t>F | 384呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t>G | 219呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I10" s="20" t="inlineStr"/>
+      <c r="J10" s="20" t="inlineStr"/>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 388呎 (2房)
+$1300万
+$33,500/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>B | 241呎 (1房)
+$851万
+$35,324/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>C | 436呎 (2房)
+$1466万
+$33,624/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>D | 270呎 (1房)
+$819万
+$30,344/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>E | 255呎 (1房)
+$802万
+$31,451/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G11" s="21" t="inlineStr">
+        <is>
+          <t>F | 384呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t>G | 219呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I11" s="20" t="inlineStr"/>
+      <c r="J11" s="20" t="inlineStr"/>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 388呎 (2房)
+$1281万
+$33,005/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 241呎 (1房)
+$840万
+$34,876/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 436呎 (2房)
+$1439万
+$33,005/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
+          <t>D | 270呎 (1房)
+$812万
+$30,093/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>E | 255呎 (1房)
+$796万
+$31,204/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G12" s="21" t="inlineStr">
+        <is>
+          <t>F | 384呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t>G | 219呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I12" s="20" t="inlineStr"/>
+      <c r="J12" s="20" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 388呎 (2房)
+$1261万
+$32,508/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>B | 241呎 (1房)
+$693万
+$28,743/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 436呎 (2房)
+$1412万
+$32,385/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
+        <is>
+          <t>D | 270呎 (1房)
+$806万
+$29,844/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F13" s="23" t="inlineStr">
+        <is>
+          <t>E | 255呎 (1房)
+$789万
+$30,953/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G13" s="23" t="inlineStr">
+        <is>
+          <t>F | 384呎 (2房)
+$1268万
+$33,018/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t>G | 219呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I13" s="20" t="inlineStr"/>
+      <c r="J13" s="20" t="inlineStr"/>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>A | 388呎 (2房)
+$1037万
+$26,727/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>B | 241呎 (1房)
+$819万
+$33,975/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 436呎 (2房)
+$1385万
+$31,764/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>D | 270呎 (1房)
+$799万
+$29,596/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F14" s="24" t="inlineStr">
+        <is>
+          <t>E | 255呎 (1房)
+$648万
+$25,412/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>F | 384呎 (2房)
+$1249万
+$32,526/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H14" s="21" t="inlineStr">
+        <is>
+          <t>G | 219呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I14" s="20" t="inlineStr"/>
+      <c r="J14" s="20" t="inlineStr"/>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>A | 388呎 (2房)
+$1224万
+$31,552/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>B | 241呎 (1房)
+$675万
+$27,996/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t>C | 436呎 (2房)
+$1365万
+$31,303/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E15" s="23" t="inlineStr">
+        <is>
+          <t>D | 270呎 (1房)
+$792万
+$29,348/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F15" s="24" t="inlineStr">
+        <is>
+          <t>E | 255呎 (1房)
+$626万
+$24,549/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>F | 384呎 (2房)
+$1230万
+$32,026/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H15" s="22" t="inlineStr">
+        <is>
+          <t>G | 219呎 (开放式)
+$724万
+$33,050/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I15" s="20" t="inlineStr"/>
+      <c r="J15" s="20" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>A | 388呎 (2房)
+$970万
+$25,000/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>B | 241呎 (1房)
+$653万
+$27,108/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>C | 436呎 (2房)
+$1155万
+$26,495/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="inlineStr">
+        <is>
+          <t>D | 270呎 (1房)
+$676万
+$25,026/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t>E | 255呎 (1房)
+$621万
+$24,349/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G16" s="23" t="inlineStr">
+        <is>
+          <t>F | 384呎 (2房)
+$1211万
+$31,529/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H16" s="23" t="inlineStr">
+        <is>
+          <t>G | 219呎 (开放式)
+$716万
+$32,680/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I16" s="20" t="inlineStr"/>
+      <c r="J16" s="20" t="inlineStr"/>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>A | 388呎 (2房)
+$954万
+$24,601/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>B | 241呎 (1房)
+$652万
+$27,037/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>C | 436呎 (2房)
+$1085万
+$24,894/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E17" s="24" t="inlineStr">
+        <is>
+          <t>D | 270呎 (1房)
+$641万
+$23,733/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F17" s="24" t="inlineStr">
+        <is>
+          <t>E | 255呎 (1房)
+$610万
+$23,922/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="inlineStr">
+        <is>
+          <t>F | 384呎 (2房)
+$1192万
+$31,034/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H17" s="22" t="inlineStr">
+        <is>
+          <t>G | 219呎 (开放式)
+$708万
+$32,306/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I17" s="20" t="inlineStr"/>
+      <c r="J17" s="20" t="inlineStr"/>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>A | 388呎 (2房)
+$974万
+$25,103/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>B | 241呎 (1房)
+$638万
+$26,490/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t>C | 436呎 (2房)
+$1278万
+$29,319/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
+        <is>
+          <t>D | 270呎 (1房)
+$772万
+$28,604/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F18" s="24" t="inlineStr">
+        <is>
+          <t>E | 255呎 (1房)
+$611万
+$23,949/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
+        <is>
+          <t>F | 384呎 (2房)
+$1173万
+$30,536/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H18" s="22" t="inlineStr">
+        <is>
+          <t>G | 219呎 (开放式)
+$699万
+$31,936/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I18" s="20" t="inlineStr"/>
+      <c r="J18" s="20" t="inlineStr"/>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>A | 388呎 (2房)
+$904万
+$23,299/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
+        <is>
+          <t>B | 241呎 (1房)
+$628万
+$26,071/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D19" s="24" t="inlineStr">
+        <is>
+          <t>C | 436呎 (2房)
+$1016万
+$23,300/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E19" s="23" t="inlineStr">
+        <is>
+          <t>D | 270呎 (1房)
+$766万
+$28,356/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F19" s="24" t="inlineStr">
+        <is>
+          <t>E | 255呎 (1房)
+$606万
+$23,749/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G19" s="23" t="inlineStr">
+        <is>
+          <t>F | 384呎 (2房)
+$1154万
+$30,039/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H19" s="23" t="inlineStr">
+        <is>
+          <t>G | 219呎 (开放式)
+$691万
+$31,566/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I19" s="20" t="inlineStr"/>
+      <c r="J19" s="20" t="inlineStr"/>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>A | 388呎 (2房)
+$1116万
+$28,758/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t>B | 241呎 (1房)
+$605万
+$25,100/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>C | 436呎 (2房)
+$1038万
+$23,819/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="inlineStr">
+        <is>
+          <t>D | 270呎 (1房)
+$756万
+$27,981/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr">
+        <is>
+          <t>E | 296呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G20" s="21" t="inlineStr">
+        <is>
+          <t>F | 346呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H20" s="22" t="inlineStr">
+        <is>
+          <t>G | 219呎 (开放式)
+$667万
+$30,470/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I20" s="20" t="inlineStr"/>
+      <c r="J20" s="20" t="inlineStr"/>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>A | 389呎 (2房)
+$922万
+$23,715/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>B | 241呎 (1房)
+$598万
+$24,801/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D21" s="23" t="inlineStr">
+        <is>
+          <t>C | 438呎 (2房)
+$1246万
+$28,447/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E21" s="23" t="inlineStr">
+        <is>
+          <t>D | 271呎 (1房)
+$748万
+$27,613/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F21" s="24" t="inlineStr">
+        <is>
+          <t>E | 276呎 (1房)
+$639万
+$23,149/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G21" s="24" t="inlineStr">
+        <is>
+          <t>F | 288呎 (1房)
+$687万
+$23,868/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H21" s="24" t="inlineStr">
+        <is>
+          <t>G | 277呎 (1房)
+$661万
+$23,870/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I21" s="23" t="inlineStr">
+        <is>
+          <t>H | 214呎 (开放式)
+$650万
+$30,369/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J21" s="22" t="inlineStr">
+        <is>
+          <t>J | 220呎 (开放式)
+$659万
+$29,964/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>A | 389呎 (2房)
+$889万
+$22,851/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>B | 241呎 (1房)
+$585万
+$24,261/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>C | 438呎 (2房)
+$994万
+$22,701/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>D | 271呎 (1房)
+$616万
+$22,742/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F22" s="24" t="inlineStr">
+        <is>
+          <t>E | 276呎 (1房)
+$631万
+$22,851/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G22" s="24" t="inlineStr">
+        <is>
+          <t>F | 288呎 (1房)
+$654万
+$22,698/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H22" s="24" t="inlineStr">
+        <is>
+          <t>G | 277呎 (1房)
+$633万
+$22,848/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I22" s="23" t="inlineStr">
+        <is>
+          <t>H | 214呎 (开放式)
+$642万
+$30,000/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J22" s="22" t="inlineStr">
+        <is>
+          <t>J | 220呎 (开放式)
+$651万
+$29,591/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>A | 389呎 (2房)
+$881万
+$22,650/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>B | 241呎 (1房)
+$583万
+$24,199/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D23" s="23" t="inlineStr">
+        <is>
+          <t>C | 438呎 (2房)
+$1227万
+$28,014/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E23" s="24" t="inlineStr">
+        <is>
+          <t>D | 271呎 (1房)
+$604万
+$22,299/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F23" s="24" t="inlineStr">
+        <is>
+          <t>E | 276呎 (1房)
+$640万
+$23,181/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="G23" s="24" t="inlineStr">
+        <is>
+          <t>F | 288呎 (1房)
+$646万
+$22,448/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H23" s="24" t="inlineStr">
+        <is>
+          <t>G | 277呎 (1房)
+$644万
+$23,249/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I23" s="23" t="inlineStr">
+        <is>
+          <t>H | 214呎 (开放式)
+$634万
+$29,626/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J23" s="22" t="inlineStr">
+        <is>
+          <t>J | 220呎 (开放式)
+$643万
+$29,223/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>A | 389呎 (2房)
+$873万
+$22,450/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>B | 241呎 (1房)
+$576万
+$23,900/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D24" s="24" t="inlineStr">
+        <is>
+          <t>C | 438呎 (2房)
+$981万
+$22,400/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="inlineStr">
+        <is>
+          <t>D | 271呎 (1房)
+$572万
+$21,114/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F24" s="24" t="inlineStr">
+        <is>
+          <t>E | 276呎 (1房)
+$608万
+$22,040/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G24" s="24" t="inlineStr">
+        <is>
+          <t>F | 288呎 (1房)
+$665万
+$23,097/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H24" s="24" t="inlineStr">
+        <is>
+          <t>G | 277呎 (1房)
+$616万
+$22,249/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I24" s="23" t="inlineStr">
+        <is>
+          <t>H | 214呎 (开放式)
+$627万
+$29,313/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J24" s="22" t="inlineStr">
+        <is>
+          <t>J | 220呎 (开放式)
+$636万
+$28,909/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>A | 389呎 (2房)
+$1075万
+$27,640/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>B | 241呎 (1房)
+$569万
+$23,602/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D25" s="23" t="inlineStr">
+        <is>
+          <t>C | 438呎 (2房)
+$1211万
+$27,642/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E25" s="24" t="inlineStr">
+        <is>
+          <t>D | 271呎 (1房)
+$564万
+$20,812/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F25" s="23" t="inlineStr">
+        <is>
+          <t>E | 276呎 (1房)
+$752万
+$27,264/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G25" s="24" t="inlineStr">
+        <is>
+          <t>F | 288呎 (1房)
+$662万
+$22,976/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H25" s="24" t="inlineStr">
+        <is>
+          <t>G | 277呎 (1房)
+$621万
+$22,422/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I25" s="23" t="inlineStr">
+        <is>
+          <t>H | 214呎 (开放式)
+$621万
+$29,005/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J25" s="23" t="inlineStr">
+        <is>
+          <t>J | 220呎 (开放式)
+$630万
+$28,632/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>A | 389呎 (2房)
+$884万
+$22,735/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
+        <is>
+          <t>B | 241呎 (1房)
+$571万
+$23,701/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D26" s="23" t="inlineStr">
+        <is>
+          <t>C | 438呎 (2房)
+$1202万
+$27,454/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E26" s="24" t="inlineStr">
+        <is>
+          <t>D | 271呎 (1房)
+$573万
+$21,159/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F26" s="24" t="inlineStr">
+        <is>
+          <t>E | 276呎 (1房)
+$614万
+$22,243/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G26" s="24" t="inlineStr">
+        <is>
+          <t>F | 288呎 (1房)
+$631万
+$21,899/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H26" s="24" t="inlineStr">
+        <is>
+          <t>G | 277呎 (1房)
+$618万
+$22,325/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I26" s="23" t="inlineStr">
+        <is>
+          <t>H | 214呎 (开放式)
+$614万
+$28,692/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J26" s="23" t="inlineStr">
+        <is>
+          <t>J | 220呎 (开放式)
+$623万
+$28,323/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>A | 389呎 (2房)
+$1054万
+$27,105/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
+        <is>
+          <t>B | 241呎 (1房)
+$571万
+$23,705/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D27" s="23" t="inlineStr">
+        <is>
+          <t>C | 438呎 (2房)
+$1194万
+$27,267/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E27" s="24" t="inlineStr">
+        <is>
+          <t>D | 271呎 (1房)
+$556万
+$20,506/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F27" s="23" t="inlineStr">
+        <is>
+          <t>E | 276呎 (1房)
+$732万
+$26,522/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G27" s="24" t="inlineStr">
+        <is>
+          <t>F | 288呎 (1房)
+$624万
+$21,649/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H27" s="24" t="inlineStr">
+        <is>
+          <t>G | 277呎 (1房)
+$586万
+$21,141/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I27" s="23" t="inlineStr">
+        <is>
+          <t>H | 214呎 (开放式)
+$606万
+$28,304/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J27" s="23" t="inlineStr">
+        <is>
+          <t>J | 220呎 (开放式)
+$616万
+$28,014/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B28" s="21" t="inlineStr">
+        <is>
+          <t>A | 350呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C28" s="21" t="inlineStr">
+        <is>
+          <t>B | 204呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D28" s="21" t="inlineStr">
+        <is>
+          <t>C | 401呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E28" s="21" t="inlineStr">
+        <is>
+          <t>D | 234呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F28" s="21" t="inlineStr">
+        <is>
+          <t>E | 238呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G28" s="21" t="inlineStr">
+        <is>
+          <t>F | 250呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H28" s="21" t="inlineStr">
+        <is>
+          <t>G | 240呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I28" s="21" t="inlineStr">
+        <is>
+          <t>H | 192呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J28" s="21" t="inlineStr">
+        <is>
+          <t>J | 199呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/港岛-香港仔及鸭脷洲-PORTO.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-PORTO.xlsx
@@ -661,7 +661,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/港岛-香港仔及鸭脷洲-PORTO.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-PORTO.xlsx
@@ -271,10 +271,10 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -651,7 +651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J176"/>
+  <dimension ref="A1:N176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -664,6 +664,10 @@
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -721,6 +725,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -771,6 +795,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -821,6 +865,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -871,6 +935,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -921,6 +1005,26 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -971,6 +1075,26 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1021,6 +1145,26 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1067,6 +1211,22 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>6988115</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>27404</v>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1113,6 +1273,22 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>7064935</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>26166</v>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1163,6 +1339,26 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1209,6 +1405,22 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>7469910</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>30995</v>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1259,6 +1471,26 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1309,6 +1541,26 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1359,6 +1611,26 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1405,6 +1677,22 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>6907955</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>27090</v>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1451,6 +1739,22 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>7008990</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>25959</v>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1501,6 +1805,26 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1547,6 +1871,22 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>7378895</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>30618</v>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1597,6 +1937,26 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1647,6 +2007,26 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1697,6 +2077,26 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1743,6 +2143,22 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>6828630</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>26779</v>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1789,6 +2205,22 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>6953045</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>25752</v>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1839,6 +2271,26 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1885,6 +2337,22 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>7288715</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>30244</v>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1931,6 +2399,22 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>11173970</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>28799</v>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1981,6 +2465,26 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2031,6 +2535,26 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2077,6 +2601,22 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>6750140</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>26471</v>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2123,6 +2663,22 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>6897100</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>25545</v>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2169,6 +2725,22 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>12467385</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>28595</v>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2215,6 +2787,22 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>7199000</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>29871</v>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2261,6 +2849,22 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>11013650</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>28386</v>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2311,6 +2915,26 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2361,6 +2985,26 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2407,6 +3051,22 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>6696700</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>26262</v>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2453,6 +3113,22 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>6841155</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>25338</v>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2499,6 +3175,22 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>12241100</v>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>28076</v>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2545,6 +3237,22 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>7108355</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>29495</v>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2591,6 +3299,22 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>10853330</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>27972</v>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2641,6 +3365,26 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2691,6 +3435,26 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2737,6 +3501,22 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>6644095</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>26055</v>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2783,6 +3563,22 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>6784375</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>25127</v>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2829,6 +3625,22 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>12015650</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>27559</v>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2875,6 +3687,22 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>7018175</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>29121</v>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2921,6 +3749,22 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>10693010</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>27559</v>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2971,6 +3815,26 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3017,6 +3881,22 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>10586965</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>27570</v>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3063,6 +3943,22 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>6590655</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>25846</v>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3109,6 +4005,22 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>6728430</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>24920</v>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3155,6 +4067,22 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>11790200</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>27042</v>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3201,6 +4129,22 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>6927000</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>28743</v>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3247,6 +4191,22 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>10531855</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>27144</v>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3297,6 +4257,26 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3343,6 +4323,22 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>10429150</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>27159</v>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3389,6 +4385,22 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>6480000</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>25412</v>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3435,6 +4447,22 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>6672485</v>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v>24713</v>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3481,6 +4509,22 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>11563915</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>26523</v>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3527,6 +4571,22 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="n">
+        <v>6836980</v>
+      </c>
+      <c r="L61" s="5" t="n">
+        <v>28369</v>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3573,6 +4633,22 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>10370000</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>26727</v>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3619,6 +4695,22 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="n">
+        <v>6043730</v>
+      </c>
+      <c r="L63" s="5" t="n">
+        <v>27597</v>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3665,6 +4757,22 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="n">
+        <v>10268830</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>26742</v>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3711,6 +4819,22 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="n">
+        <v>6260000</v>
+      </c>
+      <c r="L65" s="5" t="n">
+        <v>24549</v>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3757,6 +4881,22 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="n">
+        <v>6616540</v>
+      </c>
+      <c r="L66" s="5" t="n">
+        <v>24506</v>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3803,6 +4943,22 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="n">
+        <v>11396080</v>
+      </c>
+      <c r="L67" s="5" t="n">
+        <v>26138</v>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3849,6 +5005,22 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="n">
+        <v>6747000</v>
+      </c>
+      <c r="L68" s="5" t="n">
+        <v>27996</v>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3895,6 +5067,22 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="n">
+        <v>10222070</v>
+      </c>
+      <c r="L69" s="5" t="n">
+        <v>26346</v>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3941,6 +5129,22 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K70" s="5" t="n">
+        <v>5976095</v>
+      </c>
+      <c r="L70" s="5" t="n">
+        <v>27288</v>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3987,6 +5191,22 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="n">
+        <v>10109345</v>
+      </c>
+      <c r="L71" s="5" t="n">
+        <v>26326</v>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4033,6 +5253,22 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="n">
+        <v>6209000</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>24349</v>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4079,6 +5315,22 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="n">
+        <v>6757000</v>
+      </c>
+      <c r="L73" s="5" t="n">
+        <v>25026</v>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4125,6 +5377,22 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="n">
+        <v>11552000</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>26495</v>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4171,6 +5439,22 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="n">
+        <v>6533000</v>
+      </c>
+      <c r="L75" s="5" t="n">
+        <v>27108</v>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4217,6 +5501,22 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="n">
+        <v>9700000</v>
+      </c>
+      <c r="L76" s="5" t="n">
+        <v>25000</v>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4263,6 +5563,22 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="n">
+        <v>5907625</v>
+      </c>
+      <c r="L77" s="5" t="n">
+        <v>26975</v>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4309,6 +5625,22 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K78" s="5" t="n">
+        <v>9950695</v>
+      </c>
+      <c r="L78" s="5" t="n">
+        <v>25913</v>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4355,6 +5687,22 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="n">
+        <v>6100000</v>
+      </c>
+      <c r="L79" s="5" t="n">
+        <v>23922</v>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4401,6 +5749,22 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" s="5" t="n">
+        <v>6408000</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <v>23733</v>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4447,6 +5811,22 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="n">
+        <v>10854000</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>24894</v>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4493,6 +5873,22 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="n">
+        <v>6516000</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>27037</v>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4539,6 +5935,22 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="5" t="n">
+        <v>9545000</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>24601</v>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4585,6 +5997,22 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="n">
+        <v>5839990</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>26667</v>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4631,6 +6059,22 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K85" s="5" t="n">
+        <v>9791210</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>25498</v>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4677,6 +6121,22 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="5" t="n">
+        <v>6107000</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>23949</v>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4723,6 +6183,22 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K87" s="5" t="n">
+        <v>6448705</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>23884</v>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N87" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4769,6 +6245,22 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K88" s="5" t="n">
+        <v>10673805</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>24481</v>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4815,6 +6307,22 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K89" s="5" t="n">
+        <v>6384000</v>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v>26490</v>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4861,6 +6369,22 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="5" t="n">
+        <v>9740000</v>
+      </c>
+      <c r="L90" s="5" t="n">
+        <v>25103</v>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N90" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4907,6 +6431,22 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K91" s="5" t="n">
+        <v>5772355</v>
+      </c>
+      <c r="L91" s="5" t="n">
+        <v>26358</v>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N91" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4953,6 +6493,22 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K92" s="5" t="n">
+        <v>9631725</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>25083</v>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4999,6 +6555,22 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K93" s="5" t="n">
+        <v>6056000</v>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>23749</v>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5045,6 +6617,22 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K94" s="5" t="n">
+        <v>6392760</v>
+      </c>
+      <c r="L94" s="5" t="n">
+        <v>23677</v>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5091,6 +6679,22 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K95" s="5" t="n">
+        <v>10159000</v>
+      </c>
+      <c r="L95" s="5" t="n">
+        <v>23300</v>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5137,6 +6741,22 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="5" t="n">
+        <v>6283000</v>
+      </c>
+      <c r="L96" s="5" t="n">
+        <v>26071</v>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N96" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5183,6 +6803,22 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="5" t="n">
+        <v>9040000</v>
+      </c>
+      <c r="L97" s="5" t="n">
+        <v>23299</v>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5229,6 +6865,22 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K98" s="5" t="n">
+        <v>5571955</v>
+      </c>
+      <c r="L98" s="5" t="n">
+        <v>25443</v>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N98" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5279,6 +6931,26 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L99" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5329,6 +7001,26 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K100" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L100" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5375,6 +7067,22 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K101" s="5" t="n">
+        <v>6308425</v>
+      </c>
+      <c r="L101" s="5" t="n">
+        <v>23365</v>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N101" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5421,6 +7129,22 @@
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="5" t="n">
+        <v>10385000</v>
+      </c>
+      <c r="L102" s="5" t="n">
+        <v>23819</v>
+      </c>
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N102" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5467,6 +7191,22 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="5" t="n">
+        <v>6049000</v>
+      </c>
+      <c r="L103" s="5" t="n">
+        <v>25100</v>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5513,6 +7253,22 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K104" s="5" t="n">
+        <v>9316930</v>
+      </c>
+      <c r="L104" s="5" t="n">
+        <v>24013</v>
+      </c>
+      <c r="M104" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N104" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5559,6 +7315,22 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K105" s="5" t="n">
+        <v>5504320</v>
+      </c>
+      <c r="L105" s="5" t="n">
+        <v>25020</v>
+      </c>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N105" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5605,6 +7377,22 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K106" s="5" t="n">
+        <v>5426665</v>
+      </c>
+      <c r="L106" s="5" t="n">
+        <v>25358</v>
+      </c>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N106" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5651,6 +7439,22 @@
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" s="5" t="n">
+        <v>6612000</v>
+      </c>
+      <c r="L107" s="5" t="n">
+        <v>23870</v>
+      </c>
+      <c r="M107" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N107" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5697,6 +7501,22 @@
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K108" s="5" t="n">
+        <v>6874000</v>
+      </c>
+      <c r="L108" s="5" t="n">
+        <v>23868</v>
+      </c>
+      <c r="M108" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N108" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5743,6 +7563,22 @@
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K109" s="5" t="n">
+        <v>6389000</v>
+      </c>
+      <c r="L109" s="5" t="n">
+        <v>23149</v>
+      </c>
+      <c r="M109" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N109" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5789,6 +7625,22 @@
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K110" s="5" t="n">
+        <v>6248305</v>
+      </c>
+      <c r="L110" s="5" t="n">
+        <v>23056</v>
+      </c>
+      <c r="M110" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N110" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5835,6 +7687,22 @@
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K111" s="5" t="n">
+        <v>10404100</v>
+      </c>
+      <c r="L111" s="5" t="n">
+        <v>23754</v>
+      </c>
+      <c r="M111" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N111" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5881,6 +7749,22 @@
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K112" s="5" t="n">
+        <v>5977000</v>
+      </c>
+      <c r="L112" s="5" t="n">
+        <v>24801</v>
+      </c>
+      <c r="M112" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N112" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5927,6 +7811,22 @@
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K113" s="5" t="n">
+        <v>9225000</v>
+      </c>
+      <c r="L113" s="5" t="n">
+        <v>23715</v>
+      </c>
+      <c r="M113" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N113" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5973,6 +7873,22 @@
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K114" s="5" t="n">
+        <v>5435850</v>
+      </c>
+      <c r="L114" s="5" t="n">
+        <v>24708</v>
+      </c>
+      <c r="M114" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N114" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6019,6 +7935,22 @@
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K115" s="5" t="n">
+        <v>5360700</v>
+      </c>
+      <c r="L115" s="5" t="n">
+        <v>25050</v>
+      </c>
+      <c r="M115" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N115" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6065,6 +7997,22 @@
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K116" s="5" t="n">
+        <v>6329000</v>
+      </c>
+      <c r="L116" s="5" t="n">
+        <v>22848</v>
+      </c>
+      <c r="M116" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N116" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6111,6 +8059,22 @@
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K117" s="5" t="n">
+        <v>6537000</v>
+      </c>
+      <c r="L117" s="5" t="n">
+        <v>22698</v>
+      </c>
+      <c r="M117" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N117" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6157,6 +8121,22 @@
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K118" s="5" t="n">
+        <v>6307000</v>
+      </c>
+      <c r="L118" s="5" t="n">
+        <v>22851</v>
+      </c>
+      <c r="M118" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N118" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6203,6 +8183,22 @@
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K119" s="5" t="n">
+        <v>6163000</v>
+      </c>
+      <c r="L119" s="5" t="n">
+        <v>22742</v>
+      </c>
+      <c r="M119" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N119" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6249,6 +8245,22 @@
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K120" s="5" t="n">
+        <v>9943000</v>
+      </c>
+      <c r="L120" s="5" t="n">
+        <v>22701</v>
+      </c>
+      <c r="M120" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N120" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6295,6 +8307,22 @@
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K121" s="5" t="n">
+        <v>5847000</v>
+      </c>
+      <c r="L121" s="5" t="n">
+        <v>24261</v>
+      </c>
+      <c r="M121" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N121" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6341,6 +8369,22 @@
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K122" s="5" t="n">
+        <v>8889000</v>
+      </c>
+      <c r="L122" s="5" t="n">
+        <v>22851</v>
+      </c>
+      <c r="M122" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N122" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6387,6 +8431,22 @@
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K123" s="5" t="n">
+        <v>5368215</v>
+      </c>
+      <c r="L123" s="5" t="n">
+        <v>24401</v>
+      </c>
+      <c r="M123" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N123" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6433,6 +8493,22 @@
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K124" s="5" t="n">
+        <v>5293900</v>
+      </c>
+      <c r="L124" s="5" t="n">
+        <v>24738</v>
+      </c>
+      <c r="M124" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N124" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6479,6 +8555,22 @@
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K125" s="5" t="n">
+        <v>6440000</v>
+      </c>
+      <c r="L125" s="5" t="n">
+        <v>23249</v>
+      </c>
+      <c r="M125" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N125" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6525,6 +8617,22 @@
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" s="5" t="n">
+        <v>6465000</v>
+      </c>
+      <c r="L126" s="5" t="n">
+        <v>22448</v>
+      </c>
+      <c r="M126" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N126" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6571,6 +8679,22 @@
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="5" t="n">
+        <v>6398000</v>
+      </c>
+      <c r="L127" s="5" t="n">
+        <v>23181</v>
+      </c>
+      <c r="M127" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N127" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6617,6 +8741,22 @@
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K128" s="5" t="n">
+        <v>6043000</v>
+      </c>
+      <c r="L128" s="5" t="n">
+        <v>22299</v>
+      </c>
+      <c r="M128" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N128" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6663,6 +8803,22 @@
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K129" s="5" t="n">
+        <v>10245450</v>
+      </c>
+      <c r="L129" s="5" t="n">
+        <v>23391</v>
+      </c>
+      <c r="M129" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N129" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6709,6 +8865,22 @@
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K130" s="5" t="n">
+        <v>5832000</v>
+      </c>
+      <c r="L130" s="5" t="n">
+        <v>24199</v>
+      </c>
+      <c r="M130" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N130" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6755,6 +8927,22 @@
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K131" s="5" t="n">
+        <v>8811000</v>
+      </c>
+      <c r="L131" s="5" t="n">
+        <v>22650</v>
+      </c>
+      <c r="M131" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N131" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6801,6 +8989,22 @@
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K132" s="5" t="n">
+        <v>5310600</v>
+      </c>
+      <c r="L132" s="5" t="n">
+        <v>24139</v>
+      </c>
+      <c r="M132" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N132" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6847,6 +9051,22 @@
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K133" s="5" t="n">
+        <v>5237955</v>
+      </c>
+      <c r="L133" s="5" t="n">
+        <v>24476</v>
+      </c>
+      <c r="M133" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N133" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6893,6 +9113,22 @@
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K134" s="5" t="n">
+        <v>6163000</v>
+      </c>
+      <c r="L134" s="5" t="n">
+        <v>22249</v>
+      </c>
+      <c r="M134" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N134" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6939,6 +9175,22 @@
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K135" s="5" t="n">
+        <v>6652000</v>
+      </c>
+      <c r="L135" s="5" t="n">
+        <v>23097</v>
+      </c>
+      <c r="M135" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N135" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6985,6 +9237,22 @@
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K136" s="5" t="n">
+        <v>6083000</v>
+      </c>
+      <c r="L136" s="5" t="n">
+        <v>22040</v>
+      </c>
+      <c r="M136" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N136" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7031,6 +9299,22 @@
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K137" s="5" t="n">
+        <v>5722000</v>
+      </c>
+      <c r="L137" s="5" t="n">
+        <v>21114</v>
+      </c>
+      <c r="M137" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N137" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7077,6 +9361,22 @@
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K138" s="5" t="n">
+        <v>9811000</v>
+      </c>
+      <c r="L138" s="5" t="n">
+        <v>22400</v>
+      </c>
+      <c r="M138" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N138" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7123,6 +9423,22 @@
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K139" s="5" t="n">
+        <v>5760000</v>
+      </c>
+      <c r="L139" s="5" t="n">
+        <v>23900</v>
+      </c>
+      <c r="M139" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N139" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7169,6 +9485,22 @@
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K140" s="5" t="n">
+        <v>8733000</v>
+      </c>
+      <c r="L140" s="5" t="n">
+        <v>22450</v>
+      </c>
+      <c r="M140" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N140" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7215,6 +9547,22 @@
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K141" s="5" t="n">
+        <v>5259665</v>
+      </c>
+      <c r="L141" s="5" t="n">
+        <v>23908</v>
+      </c>
+      <c r="M141" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N141" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7261,6 +9609,22 @@
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K142" s="5" t="n">
+        <v>5182845</v>
+      </c>
+      <c r="L142" s="5" t="n">
+        <v>24219</v>
+      </c>
+      <c r="M142" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N142" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7307,6 +9671,22 @@
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K143" s="5" t="n">
+        <v>6211000</v>
+      </c>
+      <c r="L143" s="5" t="n">
+        <v>22422</v>
+      </c>
+      <c r="M143" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N143" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7353,6 +9733,22 @@
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K144" s="5" t="n">
+        <v>6617000</v>
+      </c>
+      <c r="L144" s="5" t="n">
+        <v>22976</v>
+      </c>
+      <c r="M144" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N144" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7399,6 +9795,22 @@
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K145" s="5" t="n">
+        <v>6283375</v>
+      </c>
+      <c r="L145" s="5" t="n">
+        <v>22766</v>
+      </c>
+      <c r="M145" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N145" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7445,6 +9857,22 @@
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K146" s="5" t="n">
+        <v>5640000</v>
+      </c>
+      <c r="L146" s="5" t="n">
+        <v>20812</v>
+      </c>
+      <c r="M146" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N146" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7491,6 +9919,22 @@
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K147" s="5" t="n">
+        <v>10109345</v>
+      </c>
+      <c r="L147" s="5" t="n">
+        <v>23081</v>
+      </c>
+      <c r="M147" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N147" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7537,6 +9981,22 @@
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K148" s="5" t="n">
+        <v>5688000</v>
+      </c>
+      <c r="L148" s="5" t="n">
+        <v>23602</v>
+      </c>
+      <c r="M148" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N148" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7583,6 +10043,22 @@
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K149" s="5" t="n">
+        <v>8977920</v>
+      </c>
+      <c r="L149" s="5" t="n">
+        <v>23079</v>
+      </c>
+      <c r="M149" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N149" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7629,6 +10105,22 @@
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K150" s="5" t="n">
+        <v>5202885</v>
+      </c>
+      <c r="L150" s="5" t="n">
+        <v>23649</v>
+      </c>
+      <c r="M150" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N150" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7675,6 +10167,22 @@
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K151" s="5" t="n">
+        <v>5126900</v>
+      </c>
+      <c r="L151" s="5" t="n">
+        <v>23957</v>
+      </c>
+      <c r="M151" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N151" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7721,6 +10229,22 @@
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K152" s="5" t="n">
+        <v>6184000</v>
+      </c>
+      <c r="L152" s="5" t="n">
+        <v>22325</v>
+      </c>
+      <c r="M152" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N152" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7767,6 +10291,22 @@
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K153" s="5" t="n">
+        <v>6307000</v>
+      </c>
+      <c r="L153" s="5" t="n">
+        <v>21899</v>
+      </c>
+      <c r="M153" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N153" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7813,6 +10353,22 @@
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K154" s="5" t="n">
+        <v>6139000</v>
+      </c>
+      <c r="L154" s="5" t="n">
+        <v>22243</v>
+      </c>
+      <c r="M154" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N154" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7859,6 +10415,22 @@
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K155" s="5" t="n">
+        <v>5734000</v>
+      </c>
+      <c r="L155" s="5" t="n">
+        <v>21159</v>
+      </c>
+      <c r="M155" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N155" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7905,6 +10477,22 @@
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K156" s="5" t="n">
+        <v>10040875</v>
+      </c>
+      <c r="L156" s="5" t="n">
+        <v>22924</v>
+      </c>
+      <c r="M156" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N156" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7951,6 +10539,22 @@
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K157" s="5" t="n">
+        <v>5712000</v>
+      </c>
+      <c r="L157" s="5" t="n">
+        <v>23701</v>
+      </c>
+      <c r="M157" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N157" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7997,6 +10601,22 @@
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K158" s="5" t="n">
+        <v>8844000</v>
+      </c>
+      <c r="L158" s="5" t="n">
+        <v>22735</v>
+      </c>
+      <c r="M158" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N158" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8043,6 +10663,22 @@
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K159" s="5" t="n">
+        <v>5146105</v>
+      </c>
+      <c r="L159" s="5" t="n">
+        <v>23391</v>
+      </c>
+      <c r="M159" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N159" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8089,6 +10725,22 @@
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K160" s="5" t="n">
+        <v>5057595</v>
+      </c>
+      <c r="L160" s="5" t="n">
+        <v>23634</v>
+      </c>
+      <c r="M160" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N160" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8135,6 +10787,22 @@
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K161" s="5" t="n">
+        <v>5856000</v>
+      </c>
+      <c r="L161" s="5" t="n">
+        <v>21141</v>
+      </c>
+      <c r="M161" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N161" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8181,6 +10849,22 @@
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K162" s="5" t="n">
+        <v>6235000</v>
+      </c>
+      <c r="L162" s="5" t="n">
+        <v>21649</v>
+      </c>
+      <c r="M162" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N162" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8227,6 +10911,22 @@
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K163" s="5" t="n">
+        <v>6112200</v>
+      </c>
+      <c r="L163" s="5" t="n">
+        <v>22146</v>
+      </c>
+      <c r="M163" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N163" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8273,6 +10973,22 @@
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K164" s="5" t="n">
+        <v>5557000</v>
+      </c>
+      <c r="L164" s="5" t="n">
+        <v>20506</v>
+      </c>
+      <c r="M164" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N164" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8319,6 +11035,22 @@
       </c>
       <c r="J165" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K165" s="5" t="n">
+        <v>9972405</v>
+      </c>
+      <c r="L165" s="5" t="n">
+        <v>22768</v>
+      </c>
+      <c r="M165" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N165" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8365,6 +11097,22 @@
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K166" s="5" t="n">
+        <v>5713000</v>
+      </c>
+      <c r="L166" s="5" t="n">
+        <v>23705</v>
+      </c>
+      <c r="M166" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N166" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8411,6 +11159,22 @@
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K167" s="5" t="n">
+        <v>8804240</v>
+      </c>
+      <c r="L167" s="5" t="n">
+        <v>22633</v>
+      </c>
+      <c r="M167" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N167" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8461,6 +11225,26 @@
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K168" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L168" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M168" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N168" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8511,6 +11295,26 @@
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K169" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L169" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M169" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N169" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8561,6 +11365,26 @@
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K170" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L170" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M170" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N170" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8611,6 +11435,26 @@
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K171" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L171" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M171" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N171" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8661,6 +11505,26 @@
       </c>
       <c r="J172" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K172" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L172" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M172" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N172" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8711,6 +11575,26 @@
       </c>
       <c r="J173" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K173" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L173" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M173" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N173" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8761,6 +11645,26 @@
       </c>
       <c r="J174" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K174" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L174" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M174" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N174" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8811,6 +11715,26 @@
       </c>
       <c r="J175" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L175" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M175" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N175" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8861,13 +11785,33 @@
       </c>
       <c r="J176" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K176" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L176" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M176" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N176" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -9021,12 +11965,49 @@
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
+          <t>28&amp;29</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 757呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 746呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr"/>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 644呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr"/>
+      <c r="G5" s="21" t="inlineStr"/>
+      <c r="H5" s="21" t="inlineStr"/>
+      <c r="I5" s="21" t="inlineStr"/>
+      <c r="J5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr"/>
-      <c r="C5" s="20" t="inlineStr"/>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 286呎 (1房)
 -
@@ -9034,49 +12015,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E5" s="20" t="inlineStr"/>
-      <c r="F5" s="20" t="inlineStr"/>
-      <c r="G5" s="20" t="inlineStr"/>
-      <c r="H5" s="20" t="inlineStr"/>
-      <c r="I5" s="20" t="inlineStr"/>
-      <c r="J5" s="20" t="inlineStr"/>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>28&amp;29</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t>A | 757呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="inlineStr">
-        <is>
-          <t>B | 746呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="21" t="inlineStr">
-        <is>
-          <t>D | 644呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F6" s="20" t="inlineStr"/>
-      <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="20" t="inlineStr"/>
-      <c r="I6" s="20" t="inlineStr"/>
-      <c r="J6" s="20" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr"/>
+      <c r="F6" s="21" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr"/>
+      <c r="H6" s="21" t="inlineStr"/>
+      <c r="I6" s="21" t="inlineStr"/>
+      <c r="J6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
@@ -9084,7 +12028,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 388呎 (2房)
 -
@@ -9100,7 +12044,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 436呎 (2房)
 -
@@ -9124,7 +12068,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G7" s="21" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -9132,7 +12076,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H7" s="21" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -9140,8 +12084,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I7" s="20" t="inlineStr"/>
-      <c r="J7" s="20" t="inlineStr"/>
+      <c r="I7" s="21" t="inlineStr"/>
+      <c r="J7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -9149,7 +12093,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 388呎 (2房)
 -
@@ -9165,7 +12109,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 436呎 (2房)
 -
@@ -9189,7 +12133,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G8" s="21" t="inlineStr">
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -9197,7 +12141,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H8" s="21" t="inlineStr">
+      <c r="H8" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -9205,8 +12149,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I8" s="20" t="inlineStr"/>
-      <c r="J8" s="20" t="inlineStr"/>
+      <c r="I8" s="21" t="inlineStr"/>
+      <c r="J8" s="21" t="inlineStr"/>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
@@ -9230,7 +12174,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 436呎 (2房)
 -
@@ -9254,7 +12198,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G9" s="21" t="inlineStr">
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -9262,7 +12206,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H9" s="21" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -9270,8 +12214,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I9" s="20" t="inlineStr"/>
-      <c r="J9" s="20" t="inlineStr"/>
+      <c r="I9" s="21" t="inlineStr"/>
+      <c r="J9" s="21" t="inlineStr"/>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
@@ -9292,7 +12236,7 @@
           <t>B | 241呎 (1房)
 $720万
 $29,871/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -9319,7 +12263,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G10" s="21" t="inlineStr">
+      <c r="G10" s="20" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -9327,7 +12271,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H10" s="21" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -9335,8 +12279,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I10" s="20" t="inlineStr"/>
-      <c r="J10" s="20" t="inlineStr"/>
+      <c r="I10" s="21" t="inlineStr"/>
+      <c r="J10" s="21" t="inlineStr"/>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
@@ -9384,7 +12328,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G11" s="21" t="inlineStr">
+      <c r="G11" s="20" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -9392,7 +12336,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H11" s="21" t="inlineStr">
+      <c r="H11" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -9400,8 +12344,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I11" s="20" t="inlineStr"/>
-      <c r="J11" s="20" t="inlineStr"/>
+      <c r="I11" s="21" t="inlineStr"/>
+      <c r="J11" s="21" t="inlineStr"/>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
@@ -9449,7 +12393,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G12" s="21" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -9457,7 +12401,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H12" s="21" t="inlineStr">
+      <c r="H12" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -9465,8 +12409,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I12" s="20" t="inlineStr"/>
-      <c r="J12" s="20" t="inlineStr"/>
+      <c r="I12" s="21" t="inlineStr"/>
+      <c r="J12" s="21" t="inlineStr"/>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
@@ -9487,7 +12431,7 @@
           <t>B | 241呎 (1房)
 $693万
 $28,743/呎
-(26年-06月)</t>
+(26年-06月-23日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -9522,7 +12466,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H13" s="21" t="inlineStr">
+      <c r="H13" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -9530,8 +12474,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I13" s="20" t="inlineStr"/>
-      <c r="J13" s="20" t="inlineStr"/>
+      <c r="I13" s="21" t="inlineStr"/>
+      <c r="J13" s="21" t="inlineStr"/>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -9544,7 +12488,7 @@
           <t>A | 388呎 (2房)
 $1037万
 $26,727/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -9576,7 +12520,7 @@
           <t>E | 255呎 (1房)
 $648万
 $25,412/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -9587,7 +12531,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H14" s="21" t="inlineStr">
+      <c r="H14" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -9595,8 +12539,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I14" s="20" t="inlineStr"/>
-      <c r="J14" s="20" t="inlineStr"/>
+      <c r="I14" s="21" t="inlineStr"/>
+      <c r="J14" s="21" t="inlineStr"/>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
@@ -9617,7 +12561,7 @@
           <t>B | 241呎 (1房)
 $675万
 $27,996/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
@@ -9641,7 +12585,7 @@
           <t>E | 255呎 (1房)
 $626万
 $24,549/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -9660,8 +12604,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I15" s="20" t="inlineStr"/>
-      <c r="J15" s="20" t="inlineStr"/>
+      <c r="I15" s="21" t="inlineStr"/>
+      <c r="J15" s="21" t="inlineStr"/>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
@@ -9674,7 +12618,7 @@
           <t>A | 388呎 (2房)
 $970万
 $25,000/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="C16" s="24" t="inlineStr">
@@ -9682,7 +12626,7 @@
           <t>B | 241呎 (1房)
 $653万
 $27,108/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="D16" s="24" t="inlineStr">
@@ -9690,7 +12634,7 @@
           <t>C | 436呎 (2房)
 $1155万
 $26,495/呎
-(26年-06月)</t>
+(26年-06月-28日)</t>
         </is>
       </c>
       <c r="E16" s="24" t="inlineStr">
@@ -9698,7 +12642,7 @@
           <t>D | 270呎 (1房)
 $676万
 $25,026/呎
-(26年-06月)</t>
+(26年-06月-28日)</t>
         </is>
       </c>
       <c r="F16" s="24" t="inlineStr">
@@ -9706,7 +12650,7 @@
           <t>E | 255呎 (1房)
 $621万
 $24,349/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="G16" s="23" t="inlineStr">
@@ -9725,8 +12669,8 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I16" s="20" t="inlineStr"/>
-      <c r="J16" s="20" t="inlineStr"/>
+      <c r="I16" s="21" t="inlineStr"/>
+      <c r="J16" s="21" t="inlineStr"/>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="19" t="inlineStr">
@@ -9739,7 +12683,7 @@
           <t>A | 388呎 (2房)
 $954万
 $24,601/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="C17" s="24" t="inlineStr">
@@ -9747,7 +12691,7 @@
           <t>B | 241呎 (1房)
 $652万
 $27,037/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="D17" s="24" t="inlineStr">
@@ -9755,7 +12699,7 @@
           <t>C | 436呎 (2房)
 $1085万
 $24,894/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="E17" s="24" t="inlineStr">
@@ -9763,7 +12707,7 @@
           <t>D | 270呎 (1房)
 $641万
 $23,733/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="F17" s="24" t="inlineStr">
@@ -9771,7 +12715,7 @@
           <t>E | 255呎 (1房)
 $610万
 $23,922/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -9790,8 +12734,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I17" s="20" t="inlineStr"/>
-      <c r="J17" s="20" t="inlineStr"/>
+      <c r="I17" s="21" t="inlineStr"/>
+      <c r="J17" s="21" t="inlineStr"/>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
@@ -9804,7 +12748,7 @@
           <t>A | 388呎 (2房)
 $974万
 $25,103/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="C18" s="24" t="inlineStr">
@@ -9812,7 +12756,7 @@
           <t>B | 241呎 (1房)
 $638万
 $26,490/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
@@ -9836,7 +12780,7 @@
           <t>E | 255呎 (1房)
 $611万
 $23,949/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -9855,8 +12799,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I18" s="20" t="inlineStr"/>
-      <c r="J18" s="20" t="inlineStr"/>
+      <c r="I18" s="21" t="inlineStr"/>
+      <c r="J18" s="21" t="inlineStr"/>
     </row>
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="19" t="inlineStr">
@@ -9869,7 +12813,7 @@
           <t>A | 388呎 (2房)
 $904万
 $23,299/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="C19" s="24" t="inlineStr">
@@ -9877,7 +12821,7 @@
           <t>B | 241呎 (1房)
 $628万
 $26,071/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="D19" s="24" t="inlineStr">
@@ -9885,7 +12829,7 @@
           <t>C | 436呎 (2房)
 $1016万
 $23,300/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="E19" s="23" t="inlineStr">
@@ -9901,7 +12845,7 @@
           <t>E | 255呎 (1房)
 $606万
 $23,749/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="G19" s="23" t="inlineStr">
@@ -9920,8 +12864,8 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I19" s="20" t="inlineStr"/>
-      <c r="J19" s="20" t="inlineStr"/>
+      <c r="I19" s="21" t="inlineStr"/>
+      <c r="J19" s="21" t="inlineStr"/>
     </row>
     <row r="20" ht="58" customHeight="1">
       <c r="A20" s="19" t="inlineStr">
@@ -9942,7 +12886,7 @@
           <t>B | 241呎 (1房)
 $605万
 $25,100/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="D20" s="24" t="inlineStr">
@@ -9950,7 +12894,7 @@
           <t>C | 436呎 (2房)
 $1038万
 $23,819/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="E20" s="23" t="inlineStr">
@@ -9961,7 +12905,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F20" s="21" t="inlineStr">
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>E | 296呎 (1房)
 -
@@ -9969,7 +12913,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G20" s="21" t="inlineStr">
+      <c r="G20" s="20" t="inlineStr">
         <is>
           <t>F | 346呎 (2房)
 -
@@ -9985,8 +12929,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I20" s="20" t="inlineStr"/>
-      <c r="J20" s="20" t="inlineStr"/>
+      <c r="I20" s="21" t="inlineStr"/>
+      <c r="J20" s="21" t="inlineStr"/>
     </row>
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="19" t="inlineStr">
@@ -9999,7 +12943,7 @@
           <t>A | 389呎 (2房)
 $922万
 $23,715/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="C21" s="24" t="inlineStr">
@@ -10007,7 +12951,7 @@
           <t>B | 241呎 (1房)
 $598万
 $24,801/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="D21" s="23" t="inlineStr">
@@ -10031,7 +12975,7 @@
           <t>E | 276呎 (1房)
 $639万
 $23,149/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="G21" s="24" t="inlineStr">
@@ -10039,7 +12983,7 @@
           <t>F | 288呎 (1房)
 $687万
 $23,868/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="H21" s="24" t="inlineStr">
@@ -10047,7 +12991,7 @@
           <t>G | 277呎 (1房)
 $661万
 $23,870/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="I21" s="23" t="inlineStr">
@@ -10078,7 +13022,7 @@
           <t>A | 389呎 (2房)
 $889万
 $22,851/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="C22" s="24" t="inlineStr">
@@ -10086,7 +13030,7 @@
           <t>B | 241呎 (1房)
 $585万
 $24,261/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="D22" s="24" t="inlineStr">
@@ -10094,7 +13038,7 @@
           <t>C | 438呎 (2房)
 $994万
 $22,701/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="E22" s="24" t="inlineStr">
@@ -10102,7 +13046,7 @@
           <t>D | 271呎 (1房)
 $616万
 $22,742/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="F22" s="24" t="inlineStr">
@@ -10110,7 +13054,7 @@
           <t>E | 276呎 (1房)
 $631万
 $22,851/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="G22" s="24" t="inlineStr">
@@ -10118,7 +13062,7 @@
           <t>F | 288呎 (1房)
 $654万
 $22,698/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="H22" s="24" t="inlineStr">
@@ -10126,7 +13070,7 @@
           <t>G | 277呎 (1房)
 $633万
 $22,848/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="I22" s="23" t="inlineStr">
@@ -10157,7 +13101,7 @@
           <t>A | 389呎 (2房)
 $881万
 $22,650/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="C23" s="24" t="inlineStr">
@@ -10165,7 +13109,7 @@
           <t>B | 241呎 (1房)
 $583万
 $24,199/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
@@ -10181,7 +13125,7 @@
           <t>D | 271呎 (1房)
 $604万
 $22,299/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="F23" s="24" t="inlineStr">
@@ -10189,7 +13133,7 @@
           <t>E | 276呎 (1房)
 $640万
 $23,181/呎
-(26年-07月)</t>
+(26年-07月-05日)</t>
         </is>
       </c>
       <c r="G23" s="24" t="inlineStr">
@@ -10197,7 +13141,7 @@
           <t>F | 288呎 (1房)
 $646万
 $22,448/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="H23" s="24" t="inlineStr">
@@ -10205,7 +13149,7 @@
           <t>G | 277呎 (1房)
 $644万
 $23,249/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="I23" s="23" t="inlineStr">
@@ -10236,7 +13180,7 @@
           <t>A | 389呎 (2房)
 $873万
 $22,450/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="C24" s="24" t="inlineStr">
@@ -10244,7 +13188,7 @@
           <t>B | 241呎 (1房)
 $576万
 $23,900/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="D24" s="24" t="inlineStr">
@@ -10252,7 +13196,7 @@
           <t>C | 438呎 (2房)
 $981万
 $22,400/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="E24" s="24" t="inlineStr">
@@ -10260,7 +13204,7 @@
           <t>D | 271呎 (1房)
 $572万
 $21,114/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="F24" s="24" t="inlineStr">
@@ -10268,7 +13212,7 @@
           <t>E | 276呎 (1房)
 $608万
 $22,040/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="G24" s="24" t="inlineStr">
@@ -10276,7 +13220,7 @@
           <t>F | 288呎 (1房)
 $665万
 $23,097/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="H24" s="24" t="inlineStr">
@@ -10284,7 +13228,7 @@
           <t>G | 277呎 (1房)
 $616万
 $22,249/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="I24" s="23" t="inlineStr">
@@ -10323,7 +13267,7 @@
           <t>B | 241呎 (1房)
 $569万
 $23,602/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="D25" s="23" t="inlineStr">
@@ -10339,7 +13283,7 @@
           <t>D | 271呎 (1房)
 $564万
 $20,812/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="F25" s="23" t="inlineStr">
@@ -10355,7 +13299,7 @@
           <t>F | 288呎 (1房)
 $662万
 $22,976/呎
-(26年-06月)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="H25" s="24" t="inlineStr">
@@ -10363,7 +13307,7 @@
           <t>G | 277呎 (1房)
 $621万
 $22,422/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="I25" s="23" t="inlineStr">
@@ -10394,7 +13338,7 @@
           <t>A | 389呎 (2房)
 $884万
 $22,735/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="C26" s="24" t="inlineStr">
@@ -10402,7 +13346,7 @@
           <t>B | 241呎 (1房)
 $571万
 $23,701/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="D26" s="23" t="inlineStr">
@@ -10418,7 +13362,7 @@
           <t>D | 271呎 (1房)
 $573万
 $21,159/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="F26" s="24" t="inlineStr">
@@ -10426,7 +13370,7 @@
           <t>E | 276呎 (1房)
 $614万
 $22,243/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="G26" s="24" t="inlineStr">
@@ -10434,7 +13378,7 @@
           <t>F | 288呎 (1房)
 $631万
 $21,899/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="H26" s="24" t="inlineStr">
@@ -10442,7 +13386,7 @@
           <t>G | 277呎 (1房)
 $618万
 $22,325/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="I26" s="23" t="inlineStr">
@@ -10481,7 +13425,7 @@
           <t>B | 241呎 (1房)
 $571万
 $23,705/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="D27" s="23" t="inlineStr">
@@ -10497,7 +13441,7 @@
           <t>D | 271呎 (1房)
 $556万
 $20,506/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="F27" s="23" t="inlineStr">
@@ -10513,7 +13457,7 @@
           <t>F | 288呎 (1房)
 $624万
 $21,649/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="H27" s="24" t="inlineStr">
@@ -10521,7 +13465,7 @@
           <t>G | 277呎 (1房)
 $586万
 $21,141/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="I27" s="23" t="inlineStr">
@@ -10547,7 +13491,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B28" s="21" t="inlineStr">
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>A | 350呎 (2房)
 -
@@ -10555,7 +13499,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C28" s="21" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr">
         <is>
           <t>B | 204呎 (1房)
 -
@@ -10563,7 +13507,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D28" s="21" t="inlineStr">
+      <c r="D28" s="20" t="inlineStr">
         <is>
           <t>C | 401呎 (2房)
 -
@@ -10571,7 +13515,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E28" s="21" t="inlineStr">
+      <c r="E28" s="20" t="inlineStr">
         <is>
           <t>D | 234呎 (1房)
 -
@@ -10579,7 +13523,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F28" s="21" t="inlineStr">
+      <c r="F28" s="20" t="inlineStr">
         <is>
           <t>E | 238呎 (1房)
 -
@@ -10587,7 +13531,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G28" s="21" t="inlineStr">
+      <c r="G28" s="20" t="inlineStr">
         <is>
           <t>F | 250呎 (1房)
 -
@@ -10595,7 +13539,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H28" s="21" t="inlineStr">
+      <c r="H28" s="20" t="inlineStr">
         <is>
           <t>G | 240呎 (1房)
 -
@@ -10603,7 +13547,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I28" s="21" t="inlineStr">
+      <c r="I28" s="20" t="inlineStr">
         <is>
           <t>H | 192呎 (开放式)
 -
@@ -10611,7 +13555,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J28" s="21" t="inlineStr">
+      <c r="J28" s="20" t="inlineStr">
         <is>
           <t>J | 199呎 (开放式)
 -

--- a/files/港岛-香港仔及鸭脷洲-PORTO.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-PORTO.xlsx
@@ -5304,7 +5304,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -12642,7 +12642,7 @@
           <t>D | 270呎 (1房)
 $676万
 $25,026/呎
-(26年-06月-28日)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="F16" s="24" t="inlineStr">

--- a/files/港岛-香港仔及鸭脷洲-PORTO.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-PORTO.xlsx
@@ -1211,7 +1211,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K9" s="5" t="n">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K10" s="5" t="n">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K12" s="5" t="n">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K16" s="5" t="n">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K17" s="5" t="n">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K19" s="5" t="n">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K23" s="5" t="n">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K24" s="5" t="n">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K26" s="5" t="n">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K27" s="5" t="n">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K30" s="5" t="n">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K31" s="5" t="n">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K32" s="5" t="n">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K34" s="5" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K37" s="5" t="n">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K38" s="5" t="n">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K39" s="5" t="n">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K40" s="5" t="n">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K41" s="5" t="n">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K44" s="5" t="n">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K45" s="5" t="n">
@@ -3625,7 +3625,7 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K46" s="5" t="n">
@@ -3687,7 +3687,7 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K47" s="5" t="n">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K48" s="5" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K50" s="5" t="n">
@@ -3943,7 +3943,7 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K51" s="5" t="n">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K52" s="5" t="n">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K53" s="5" t="n">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K55" s="5" t="n">
@@ -4323,7 +4323,7 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K57" s="5" t="n">
@@ -4447,7 +4447,7 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K59" s="5" t="n">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K60" s="5" t="n">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K61" s="5" t="n">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K63" s="5" t="n">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K64" s="5" t="n">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K66" s="5" t="n">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K67" s="5" t="n">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K69" s="5" t="n">
@@ -5129,7 +5129,7 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K70" s="5" t="n">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K71" s="5" t="n">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K77" s="5" t="n">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K78" s="5" t="n">
@@ -5997,7 +5997,7 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K84" s="5" t="n">
@@ -6059,7 +6059,7 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K85" s="5" t="n">
@@ -6183,7 +6183,7 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K87" s="5" t="n">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K88" s="5" t="n">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K91" s="5" t="n">
@@ -6493,7 +6493,7 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K92" s="5" t="n">
@@ -6617,7 +6617,7 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K94" s="5" t="n">
@@ -6865,7 +6865,7 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K98" s="5" t="n">
@@ -7067,7 +7067,7 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K101" s="5" t="n">
@@ -7253,7 +7253,7 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K104" s="5" t="n">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K105" s="5" t="n">
@@ -7377,7 +7377,7 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K106" s="5" t="n">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K110" s="5" t="n">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K111" s="5" t="n">
@@ -7873,7 +7873,7 @@
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K114" s="5" t="n">
@@ -7935,7 +7935,7 @@
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K115" s="5" t="n">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K123" s="5" t="n">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K124" s="5" t="n">
@@ -8803,7 +8803,7 @@
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K129" s="5" t="n">
@@ -8989,7 +8989,7 @@
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K132" s="5" t="n">
@@ -9051,7 +9051,7 @@
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K133" s="5" t="n">
@@ -9547,7 +9547,7 @@
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K141" s="5" t="n">
@@ -9609,7 +9609,7 @@
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K142" s="5" t="n">
@@ -9795,7 +9795,7 @@
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K145" s="5" t="n">
@@ -9919,7 +9919,7 @@
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K147" s="5" t="n">
@@ -10043,7 +10043,7 @@
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K149" s="5" t="n">
@@ -10105,7 +10105,7 @@
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K150" s="5" t="n">
@@ -10167,7 +10167,7 @@
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K151" s="5" t="n">
@@ -10477,7 +10477,7 @@
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K156" s="5" t="n">
@@ -10663,7 +10663,7 @@
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K159" s="5" t="n">
@@ -10725,7 +10725,7 @@
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K160" s="5" t="n">
@@ -10911,7 +10911,7 @@
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K163" s="5" t="n">
@@ -11035,7 +11035,7 @@
       </c>
       <c r="J165" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K165" s="5" t="n">
@@ -11159,7 +11159,7 @@
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="K167" s="5" t="n">

--- a/files/港岛-香港仔及鸭脷洲-PORTO.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-PORTO.xlsx
@@ -271,10 +271,10 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -11965,10 +11965,33 @@
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>C | 286呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr"/>
+      <c r="F5" s="20" t="inlineStr"/>
+      <c r="G5" s="20" t="inlineStr"/>
+      <c r="H5" s="20" t="inlineStr"/>
+      <c r="I5" s="20" t="inlineStr"/>
+      <c r="J5" s="20" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
           <t>28&amp;29</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>A | 757呎 (3房)
 -
@@ -11976,7 +11999,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>B | 746呎 (3房)
 -
@@ -11984,8 +12007,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr"/>
-      <c r="E5" s="20" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr">
         <is>
           <t>D | 644呎 (2房)
 -
@@ -11993,34 +12016,11 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F5" s="21" t="inlineStr"/>
-      <c r="G5" s="21" t="inlineStr"/>
-      <c r="H5" s="21" t="inlineStr"/>
-      <c r="I5" s="21" t="inlineStr"/>
-      <c r="J5" s="21" t="inlineStr"/>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr">
-        <is>
-          <t>C | 286呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E6" s="21" t="inlineStr"/>
-      <c r="F6" s="21" t="inlineStr"/>
-      <c r="G6" s="21" t="inlineStr"/>
-      <c r="H6" s="21" t="inlineStr"/>
-      <c r="I6" s="21" t="inlineStr"/>
-      <c r="J6" s="21" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="20" t="inlineStr"/>
+      <c r="H6" s="20" t="inlineStr"/>
+      <c r="I6" s="20" t="inlineStr"/>
+      <c r="J6" s="20" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
@@ -12028,7 +12028,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 388呎 (2房)
 -
@@ -12044,7 +12044,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 436呎 (2房)
 -
@@ -12068,7 +12068,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G7" s="20" t="inlineStr">
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12076,7 +12076,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H7" s="20" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12084,8 +12084,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I7" s="21" t="inlineStr"/>
-      <c r="J7" s="21" t="inlineStr"/>
+      <c r="I7" s="20" t="inlineStr"/>
+      <c r="J7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -12093,7 +12093,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>A | 388呎 (2房)
 -
@@ -12109,7 +12109,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>C | 436呎 (2房)
 -
@@ -12133,7 +12133,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G8" s="20" t="inlineStr">
+      <c r="G8" s="21" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12141,7 +12141,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H8" s="20" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12149,8 +12149,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I8" s="21" t="inlineStr"/>
-      <c r="J8" s="21" t="inlineStr"/>
+      <c r="I8" s="20" t="inlineStr"/>
+      <c r="J8" s="20" t="inlineStr"/>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
@@ -12174,7 +12174,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>C | 436呎 (2房)
 -
@@ -12198,7 +12198,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G9" s="20" t="inlineStr">
+      <c r="G9" s="21" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12206,7 +12206,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H9" s="20" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12214,8 +12214,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I9" s="21" t="inlineStr"/>
-      <c r="J9" s="21" t="inlineStr"/>
+      <c r="I9" s="20" t="inlineStr"/>
+      <c r="J9" s="20" t="inlineStr"/>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
@@ -12263,7 +12263,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G10" s="20" t="inlineStr">
+      <c r="G10" s="21" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12271,7 +12271,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H10" s="20" t="inlineStr">
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12279,8 +12279,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I10" s="21" t="inlineStr"/>
-      <c r="J10" s="21" t="inlineStr"/>
+      <c r="I10" s="20" t="inlineStr"/>
+      <c r="J10" s="20" t="inlineStr"/>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
@@ -12328,7 +12328,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G11" s="20" t="inlineStr">
+      <c r="G11" s="21" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12336,7 +12336,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H11" s="20" t="inlineStr">
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12344,8 +12344,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I11" s="21" t="inlineStr"/>
-      <c r="J11" s="21" t="inlineStr"/>
+      <c r="I11" s="20" t="inlineStr"/>
+      <c r="J11" s="20" t="inlineStr"/>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
@@ -12393,7 +12393,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G12" s="20" t="inlineStr">
+      <c r="G12" s="21" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12401,7 +12401,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H12" s="20" t="inlineStr">
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12409,8 +12409,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I12" s="21" t="inlineStr"/>
-      <c r="J12" s="21" t="inlineStr"/>
+      <c r="I12" s="20" t="inlineStr"/>
+      <c r="J12" s="20" t="inlineStr"/>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
@@ -12466,7 +12466,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H13" s="20" t="inlineStr">
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12474,8 +12474,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I13" s="21" t="inlineStr"/>
-      <c r="J13" s="21" t="inlineStr"/>
+      <c r="I13" s="20" t="inlineStr"/>
+      <c r="J13" s="20" t="inlineStr"/>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -12531,7 +12531,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H14" s="20" t="inlineStr">
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12539,8 +12539,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I14" s="21" t="inlineStr"/>
-      <c r="J14" s="21" t="inlineStr"/>
+      <c r="I14" s="20" t="inlineStr"/>
+      <c r="J14" s="20" t="inlineStr"/>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
@@ -12604,8 +12604,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I15" s="21" t="inlineStr"/>
-      <c r="J15" s="21" t="inlineStr"/>
+      <c r="I15" s="20" t="inlineStr"/>
+      <c r="J15" s="20" t="inlineStr"/>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
@@ -12634,7 +12634,7 @@
           <t>C | 436呎 (2房)
 $1155万
 $26,495/呎
-(26年-06月-28日)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="E16" s="24" t="inlineStr">
@@ -12669,8 +12669,8 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I16" s="21" t="inlineStr"/>
-      <c r="J16" s="21" t="inlineStr"/>
+      <c r="I16" s="20" t="inlineStr"/>
+      <c r="J16" s="20" t="inlineStr"/>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="19" t="inlineStr">
@@ -12734,8 +12734,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I17" s="21" t="inlineStr"/>
-      <c r="J17" s="21" t="inlineStr"/>
+      <c r="I17" s="20" t="inlineStr"/>
+      <c r="J17" s="20" t="inlineStr"/>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
@@ -12799,8 +12799,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I18" s="21" t="inlineStr"/>
-      <c r="J18" s="21" t="inlineStr"/>
+      <c r="I18" s="20" t="inlineStr"/>
+      <c r="J18" s="20" t="inlineStr"/>
     </row>
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="19" t="inlineStr">
@@ -12864,8 +12864,8 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I19" s="21" t="inlineStr"/>
-      <c r="J19" s="21" t="inlineStr"/>
+      <c r="I19" s="20" t="inlineStr"/>
+      <c r="J19" s="20" t="inlineStr"/>
     </row>
     <row r="20" ht="58" customHeight="1">
       <c r="A20" s="19" t="inlineStr">
@@ -12905,7 +12905,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F20" s="20" t="inlineStr">
+      <c r="F20" s="21" t="inlineStr">
         <is>
           <t>E | 296呎 (1房)
 -
@@ -12913,7 +12913,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G20" s="20" t="inlineStr">
+      <c r="G20" s="21" t="inlineStr">
         <is>
           <t>F | 346呎 (2房)
 -
@@ -12929,8 +12929,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I20" s="21" t="inlineStr"/>
-      <c r="J20" s="21" t="inlineStr"/>
+      <c r="I20" s="20" t="inlineStr"/>
+      <c r="J20" s="20" t="inlineStr"/>
     </row>
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="19" t="inlineStr">
@@ -13491,7 +13491,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B28" s="20" t="inlineStr">
+      <c r="B28" s="21" t="inlineStr">
         <is>
           <t>A | 350呎 (2房)
 -
@@ -13499,7 +13499,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C28" s="20" t="inlineStr">
+      <c r="C28" s="21" t="inlineStr">
         <is>
           <t>B | 204呎 (1房)
 -
@@ -13507,7 +13507,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D28" s="20" t="inlineStr">
+      <c r="D28" s="21" t="inlineStr">
         <is>
           <t>C | 401呎 (2房)
 -
@@ -13515,7 +13515,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E28" s="20" t="inlineStr">
+      <c r="E28" s="21" t="inlineStr">
         <is>
           <t>D | 234呎 (1房)
 -
@@ -13523,7 +13523,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F28" s="20" t="inlineStr">
+      <c r="F28" s="21" t="inlineStr">
         <is>
           <t>E | 238呎 (1房)
 -
@@ -13531,7 +13531,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G28" s="20" t="inlineStr">
+      <c r="G28" s="21" t="inlineStr">
         <is>
           <t>F | 250呎 (1房)
 -
@@ -13539,7 +13539,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H28" s="20" t="inlineStr">
+      <c r="H28" s="21" t="inlineStr">
         <is>
           <t>G | 240呎 (1房)
 -
@@ -13547,7 +13547,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I28" s="20" t="inlineStr">
+      <c r="I28" s="21" t="inlineStr">
         <is>
           <t>H | 192呎 (开放式)
 -
@@ -13555,7 +13555,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J28" s="20" t="inlineStr">
+      <c r="J28" s="21" t="inlineStr">
         <is>
           <t>J | 199呎 (开放式)
 -

--- a/files/港岛-香港仔及鸭脷洲-PORTO.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-PORTO.xlsx
@@ -271,10 +271,10 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -11965,12 +11965,49 @@
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
+          <t>28&amp;29</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 757呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 746呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr"/>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 644呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr"/>
+      <c r="G5" s="21" t="inlineStr"/>
+      <c r="H5" s="21" t="inlineStr"/>
+      <c r="I5" s="21" t="inlineStr"/>
+      <c r="J5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr"/>
-      <c r="C5" s="20" t="inlineStr"/>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 286呎 (1房)
 -
@@ -11978,49 +12015,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E5" s="20" t="inlineStr"/>
-      <c r="F5" s="20" t="inlineStr"/>
-      <c r="G5" s="20" t="inlineStr"/>
-      <c r="H5" s="20" t="inlineStr"/>
-      <c r="I5" s="20" t="inlineStr"/>
-      <c r="J5" s="20" t="inlineStr"/>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>28&amp;29</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t>A | 757呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="inlineStr">
-        <is>
-          <t>B | 746呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="21" t="inlineStr">
-        <is>
-          <t>D | 644呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F6" s="20" t="inlineStr"/>
-      <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="20" t="inlineStr"/>
-      <c r="I6" s="20" t="inlineStr"/>
-      <c r="J6" s="20" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr"/>
+      <c r="F6" s="21" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr"/>
+      <c r="H6" s="21" t="inlineStr"/>
+      <c r="I6" s="21" t="inlineStr"/>
+      <c r="J6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
@@ -12028,7 +12028,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 388呎 (2房)
 -
@@ -12044,7 +12044,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 436呎 (2房)
 -
@@ -12068,7 +12068,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G7" s="21" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12076,7 +12076,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H7" s="21" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12084,8 +12084,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I7" s="20" t="inlineStr"/>
-      <c r="J7" s="20" t="inlineStr"/>
+      <c r="I7" s="21" t="inlineStr"/>
+      <c r="J7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -12093,7 +12093,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 388呎 (2房)
 -
@@ -12109,7 +12109,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 436呎 (2房)
 -
@@ -12133,7 +12133,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G8" s="21" t="inlineStr">
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12141,7 +12141,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H8" s="21" t="inlineStr">
+      <c r="H8" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12149,8 +12149,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I8" s="20" t="inlineStr"/>
-      <c r="J8" s="20" t="inlineStr"/>
+      <c r="I8" s="21" t="inlineStr"/>
+      <c r="J8" s="21" t="inlineStr"/>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
@@ -12174,7 +12174,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 436呎 (2房)
 -
@@ -12198,7 +12198,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G9" s="21" t="inlineStr">
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12206,7 +12206,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H9" s="21" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12214,8 +12214,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I9" s="20" t="inlineStr"/>
-      <c r="J9" s="20" t="inlineStr"/>
+      <c r="I9" s="21" t="inlineStr"/>
+      <c r="J9" s="21" t="inlineStr"/>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
@@ -12236,7 +12236,7 @@
           <t>B | 241呎 (1房)
 $720万
 $29,871/呎
-(26年-07月-07日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -12263,7 +12263,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G10" s="21" t="inlineStr">
+      <c r="G10" s="20" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12271,7 +12271,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H10" s="21" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12279,8 +12279,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I10" s="20" t="inlineStr"/>
-      <c r="J10" s="20" t="inlineStr"/>
+      <c r="I10" s="21" t="inlineStr"/>
+      <c r="J10" s="21" t="inlineStr"/>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
@@ -12328,7 +12328,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G11" s="21" t="inlineStr">
+      <c r="G11" s="20" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12336,7 +12336,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H11" s="21" t="inlineStr">
+      <c r="H11" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12344,8 +12344,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I11" s="20" t="inlineStr"/>
-      <c r="J11" s="20" t="inlineStr"/>
+      <c r="I11" s="21" t="inlineStr"/>
+      <c r="J11" s="21" t="inlineStr"/>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
@@ -12393,7 +12393,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G12" s="21" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12401,7 +12401,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H12" s="21" t="inlineStr">
+      <c r="H12" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12409,8 +12409,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I12" s="20" t="inlineStr"/>
-      <c r="J12" s="20" t="inlineStr"/>
+      <c r="I12" s="21" t="inlineStr"/>
+      <c r="J12" s="21" t="inlineStr"/>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
@@ -12431,7 +12431,7 @@
           <t>B | 241呎 (1房)
 $693万
 $28,743/呎
-(26年-06月-23日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -12466,7 +12466,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H13" s="21" t="inlineStr">
+      <c r="H13" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12474,8 +12474,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I13" s="20" t="inlineStr"/>
-      <c r="J13" s="20" t="inlineStr"/>
+      <c r="I13" s="21" t="inlineStr"/>
+      <c r="J13" s="21" t="inlineStr"/>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -12488,7 +12488,7 @@
           <t>A | 388呎 (2房)
 $1037万
 $26,727/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -12520,7 +12520,7 @@
           <t>E | 255呎 (1房)
 $648万
 $25,412/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -12531,7 +12531,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H14" s="21" t="inlineStr">
+      <c r="H14" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12539,8 +12539,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I14" s="20" t="inlineStr"/>
-      <c r="J14" s="20" t="inlineStr"/>
+      <c r="I14" s="21" t="inlineStr"/>
+      <c r="J14" s="21" t="inlineStr"/>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
@@ -12561,7 +12561,7 @@
           <t>B | 241呎 (1房)
 $675万
 $27,996/呎
-(26年-07月-07日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
@@ -12585,7 +12585,7 @@
           <t>E | 255呎 (1房)
 $626万
 $24,549/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -12604,8 +12604,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I15" s="20" t="inlineStr"/>
-      <c r="J15" s="20" t="inlineStr"/>
+      <c r="I15" s="21" t="inlineStr"/>
+      <c r="J15" s="21" t="inlineStr"/>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
@@ -12618,7 +12618,7 @@
           <t>A | 388呎 (2房)
 $970万
 $25,000/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C16" s="24" t="inlineStr">
@@ -12626,7 +12626,7 @@
           <t>B | 241呎 (1房)
 $653万
 $27,108/呎
-(26年-06月-10日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D16" s="24" t="inlineStr">
@@ -12634,7 +12634,7 @@
           <t>C | 436呎 (2房)
 $1155万
 $26,495/呎
-(26年-07月-15日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E16" s="24" t="inlineStr">
@@ -12642,7 +12642,7 @@
           <t>D | 270呎 (1房)
 $676万
 $25,026/呎
-(26年-07月-13日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F16" s="24" t="inlineStr">
@@ -12650,7 +12650,7 @@
           <t>E | 255呎 (1房)
 $621万
 $24,349/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G16" s="23" t="inlineStr">
@@ -12669,8 +12669,8 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I16" s="20" t="inlineStr"/>
-      <c r="J16" s="20" t="inlineStr"/>
+      <c r="I16" s="21" t="inlineStr"/>
+      <c r="J16" s="21" t="inlineStr"/>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="19" t="inlineStr">
@@ -12683,7 +12683,7 @@
           <t>A | 388呎 (2房)
 $954万
 $24,601/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C17" s="24" t="inlineStr">
@@ -12691,7 +12691,7 @@
           <t>B | 241呎 (1房)
 $652万
 $27,037/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D17" s="24" t="inlineStr">
@@ -12699,7 +12699,7 @@
           <t>C | 436呎 (2房)
 $1085万
 $24,894/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E17" s="24" t="inlineStr">
@@ -12707,7 +12707,7 @@
           <t>D | 270呎 (1房)
 $641万
 $23,733/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F17" s="24" t="inlineStr">
@@ -12715,7 +12715,7 @@
           <t>E | 255呎 (1房)
 $610万
 $23,922/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -12734,8 +12734,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I17" s="20" t="inlineStr"/>
-      <c r="J17" s="20" t="inlineStr"/>
+      <c r="I17" s="21" t="inlineStr"/>
+      <c r="J17" s="21" t="inlineStr"/>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
@@ -12748,7 +12748,7 @@
           <t>A | 388呎 (2房)
 $974万
 $25,103/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C18" s="24" t="inlineStr">
@@ -12756,7 +12756,7 @@
           <t>B | 241呎 (1房)
 $638万
 $26,490/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
@@ -12780,7 +12780,7 @@
           <t>E | 255呎 (1房)
 $611万
 $23,949/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -12799,8 +12799,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I18" s="20" t="inlineStr"/>
-      <c r="J18" s="20" t="inlineStr"/>
+      <c r="I18" s="21" t="inlineStr"/>
+      <c r="J18" s="21" t="inlineStr"/>
     </row>
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="19" t="inlineStr">
@@ -12813,7 +12813,7 @@
           <t>A | 388呎 (2房)
 $904万
 $23,299/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C19" s="24" t="inlineStr">
@@ -12821,7 +12821,7 @@
           <t>B | 241呎 (1房)
 $628万
 $26,071/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D19" s="24" t="inlineStr">
@@ -12829,7 +12829,7 @@
           <t>C | 436呎 (2房)
 $1016万
 $23,300/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E19" s="23" t="inlineStr">
@@ -12845,7 +12845,7 @@
           <t>E | 255呎 (1房)
 $606万
 $23,749/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G19" s="23" t="inlineStr">
@@ -12864,8 +12864,8 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I19" s="20" t="inlineStr"/>
-      <c r="J19" s="20" t="inlineStr"/>
+      <c r="I19" s="21" t="inlineStr"/>
+      <c r="J19" s="21" t="inlineStr"/>
     </row>
     <row r="20" ht="58" customHeight="1">
       <c r="A20" s="19" t="inlineStr">
@@ -12886,7 +12886,7 @@
           <t>B | 241呎 (1房)
 $605万
 $25,100/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D20" s="24" t="inlineStr">
@@ -12894,7 +12894,7 @@
           <t>C | 436呎 (2房)
 $1038万
 $23,819/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E20" s="23" t="inlineStr">
@@ -12905,7 +12905,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F20" s="21" t="inlineStr">
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>E | 296呎 (1房)
 -
@@ -12913,7 +12913,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G20" s="21" t="inlineStr">
+      <c r="G20" s="20" t="inlineStr">
         <is>
           <t>F | 346呎 (2房)
 -
@@ -12929,8 +12929,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I20" s="20" t="inlineStr"/>
-      <c r="J20" s="20" t="inlineStr"/>
+      <c r="I20" s="21" t="inlineStr"/>
+      <c r="J20" s="21" t="inlineStr"/>
     </row>
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="19" t="inlineStr">
@@ -12943,7 +12943,7 @@
           <t>A | 389呎 (2房)
 $922万
 $23,715/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C21" s="24" t="inlineStr">
@@ -12951,7 +12951,7 @@
           <t>B | 241呎 (1房)
 $598万
 $24,801/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D21" s="23" t="inlineStr">
@@ -12975,7 +12975,7 @@
           <t>E | 276呎 (1房)
 $639万
 $23,149/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G21" s="24" t="inlineStr">
@@ -12983,7 +12983,7 @@
           <t>F | 288呎 (1房)
 $687万
 $23,868/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="H21" s="24" t="inlineStr">
@@ -12991,7 +12991,7 @@
           <t>G | 277呎 (1房)
 $661万
 $23,870/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I21" s="23" t="inlineStr">
@@ -13022,7 +13022,7 @@
           <t>A | 389呎 (2房)
 $889万
 $22,851/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C22" s="24" t="inlineStr">
@@ -13030,7 +13030,7 @@
           <t>B | 241呎 (1房)
 $585万
 $24,261/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D22" s="24" t="inlineStr">
@@ -13038,7 +13038,7 @@
           <t>C | 438呎 (2房)
 $994万
 $22,701/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E22" s="24" t="inlineStr">
@@ -13046,7 +13046,7 @@
           <t>D | 271呎 (1房)
 $616万
 $22,742/呎
-(26年-06月-10日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F22" s="24" t="inlineStr">
@@ -13054,7 +13054,7 @@
           <t>E | 276呎 (1房)
 $631万
 $22,851/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G22" s="24" t="inlineStr">
@@ -13062,7 +13062,7 @@
           <t>F | 288呎 (1房)
 $654万
 $22,698/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H22" s="24" t="inlineStr">
@@ -13070,7 +13070,7 @@
           <t>G | 277呎 (1房)
 $633万
 $22,848/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I22" s="23" t="inlineStr">
@@ -13101,7 +13101,7 @@
           <t>A | 389呎 (2房)
 $881万
 $22,650/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C23" s="24" t="inlineStr">
@@ -13109,7 +13109,7 @@
           <t>B | 241呎 (1房)
 $583万
 $24,199/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
@@ -13125,7 +13125,7 @@
           <t>D | 271呎 (1房)
 $604万
 $22,299/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F23" s="24" t="inlineStr">
@@ -13133,7 +13133,7 @@
           <t>E | 276呎 (1房)
 $640万
 $23,181/呎
-(26年-07月-05日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="G23" s="24" t="inlineStr">
@@ -13141,7 +13141,7 @@
           <t>F | 288呎 (1房)
 $646万
 $22,448/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H23" s="24" t="inlineStr">
@@ -13149,7 +13149,7 @@
           <t>G | 277呎 (1房)
 $644万
 $23,249/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I23" s="23" t="inlineStr">
@@ -13180,7 +13180,7 @@
           <t>A | 389呎 (2房)
 $873万
 $22,450/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C24" s="24" t="inlineStr">
@@ -13188,7 +13188,7 @@
           <t>B | 241呎 (1房)
 $576万
 $23,900/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D24" s="24" t="inlineStr">
@@ -13196,7 +13196,7 @@
           <t>C | 438呎 (2房)
 $981万
 $22,400/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E24" s="24" t="inlineStr">
@@ -13204,7 +13204,7 @@
           <t>D | 271呎 (1房)
 $572万
 $21,114/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F24" s="24" t="inlineStr">
@@ -13212,7 +13212,7 @@
           <t>E | 276呎 (1房)
 $608万
 $22,040/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G24" s="24" t="inlineStr">
@@ -13220,7 +13220,7 @@
           <t>F | 288呎 (1房)
 $665万
 $23,097/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H24" s="24" t="inlineStr">
@@ -13228,7 +13228,7 @@
           <t>G | 277呎 (1房)
 $616万
 $22,249/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I24" s="23" t="inlineStr">
@@ -13267,7 +13267,7 @@
           <t>B | 241呎 (1房)
 $569万
 $23,602/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D25" s="23" t="inlineStr">
@@ -13283,7 +13283,7 @@
           <t>D | 271呎 (1房)
 $564万
 $20,812/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F25" s="23" t="inlineStr">
@@ -13299,7 +13299,7 @@
           <t>F | 288呎 (1房)
 $662万
 $22,976/呎
-(26年-06月-17日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="H25" s="24" t="inlineStr">
@@ -13307,7 +13307,7 @@
           <t>G | 277呎 (1房)
 $621万
 $22,422/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I25" s="23" t="inlineStr">
@@ -13338,7 +13338,7 @@
           <t>A | 389呎 (2房)
 $884万
 $22,735/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C26" s="24" t="inlineStr">
@@ -13346,7 +13346,7 @@
           <t>B | 241呎 (1房)
 $571万
 $23,701/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D26" s="23" t="inlineStr">
@@ -13362,7 +13362,7 @@
           <t>D | 271呎 (1房)
 $573万
 $21,159/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F26" s="24" t="inlineStr">
@@ -13370,7 +13370,7 @@
           <t>E | 276呎 (1房)
 $614万
 $22,243/呎
-(26年-06月-10日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G26" s="24" t="inlineStr">
@@ -13378,7 +13378,7 @@
           <t>F | 288呎 (1房)
 $631万
 $21,899/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="H26" s="24" t="inlineStr">
@@ -13386,7 +13386,7 @@
           <t>G | 277呎 (1房)
 $618万
 $22,325/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I26" s="23" t="inlineStr">
@@ -13425,7 +13425,7 @@
           <t>B | 241呎 (1房)
 $571万
 $23,705/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D27" s="23" t="inlineStr">
@@ -13441,7 +13441,7 @@
           <t>D | 271呎 (1房)
 $556万
 $20,506/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F27" s="23" t="inlineStr">
@@ -13457,7 +13457,7 @@
           <t>F | 288呎 (1房)
 $624万
 $21,649/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H27" s="24" t="inlineStr">
@@ -13465,7 +13465,7 @@
           <t>G | 277呎 (1房)
 $586万
 $21,141/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I27" s="23" t="inlineStr">
@@ -13491,7 +13491,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B28" s="21" t="inlineStr">
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>A | 350呎 (2房)
 -
@@ -13499,7 +13499,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C28" s="21" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr">
         <is>
           <t>B | 204呎 (1房)
 -
@@ -13507,7 +13507,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D28" s="21" t="inlineStr">
+      <c r="D28" s="20" t="inlineStr">
         <is>
           <t>C | 401呎 (2房)
 -
@@ -13515,7 +13515,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E28" s="21" t="inlineStr">
+      <c r="E28" s="20" t="inlineStr">
         <is>
           <t>D | 234呎 (1房)
 -
@@ -13523,7 +13523,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F28" s="21" t="inlineStr">
+      <c r="F28" s="20" t="inlineStr">
         <is>
           <t>E | 238呎 (1房)
 -
@@ -13531,7 +13531,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G28" s="21" t="inlineStr">
+      <c r="G28" s="20" t="inlineStr">
         <is>
           <t>F | 250呎 (1房)
 -
@@ -13539,7 +13539,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H28" s="21" t="inlineStr">
+      <c r="H28" s="20" t="inlineStr">
         <is>
           <t>G | 240呎 (1房)
 -
@@ -13547,7 +13547,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I28" s="21" t="inlineStr">
+      <c r="I28" s="20" t="inlineStr">
         <is>
           <t>H | 192呎 (开放式)
 -
@@ -13555,7 +13555,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J28" s="21" t="inlineStr">
+      <c r="J28" s="20" t="inlineStr">
         <is>
           <t>J | 199呎 (开放式)
 -

--- a/files/港岛-香港仔及鸭脷洲-PORTO.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-PORTO.xlsx
@@ -271,10 +271,10 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -11965,10 +11965,33 @@
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>C | 286呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr"/>
+      <c r="F5" s="20" t="inlineStr"/>
+      <c r="G5" s="20" t="inlineStr"/>
+      <c r="H5" s="20" t="inlineStr"/>
+      <c r="I5" s="20" t="inlineStr"/>
+      <c r="J5" s="20" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
           <t>28&amp;29</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>A | 757呎 (3房)
 -
@@ -11976,7 +11999,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>B | 746呎 (3房)
 -
@@ -11984,8 +12007,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr"/>
-      <c r="E5" s="20" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr">
         <is>
           <t>D | 644呎 (2房)
 -
@@ -11993,34 +12016,11 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F5" s="21" t="inlineStr"/>
-      <c r="G5" s="21" t="inlineStr"/>
-      <c r="H5" s="21" t="inlineStr"/>
-      <c r="I5" s="21" t="inlineStr"/>
-      <c r="J5" s="21" t="inlineStr"/>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr">
-        <is>
-          <t>C | 286呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E6" s="21" t="inlineStr"/>
-      <c r="F6" s="21" t="inlineStr"/>
-      <c r="G6" s="21" t="inlineStr"/>
-      <c r="H6" s="21" t="inlineStr"/>
-      <c r="I6" s="21" t="inlineStr"/>
-      <c r="J6" s="21" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="20" t="inlineStr"/>
+      <c r="H6" s="20" t="inlineStr"/>
+      <c r="I6" s="20" t="inlineStr"/>
+      <c r="J6" s="20" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
@@ -12028,7 +12028,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 388呎 (2房)
 -
@@ -12044,7 +12044,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 436呎 (2房)
 -
@@ -12068,7 +12068,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G7" s="20" t="inlineStr">
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12076,7 +12076,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H7" s="20" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12084,8 +12084,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I7" s="21" t="inlineStr"/>
-      <c r="J7" s="21" t="inlineStr"/>
+      <c r="I7" s="20" t="inlineStr"/>
+      <c r="J7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -12093,7 +12093,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>A | 388呎 (2房)
 -
@@ -12109,7 +12109,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>C | 436呎 (2房)
 -
@@ -12133,7 +12133,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G8" s="20" t="inlineStr">
+      <c r="G8" s="21" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12141,7 +12141,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H8" s="20" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12149,8 +12149,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I8" s="21" t="inlineStr"/>
-      <c r="J8" s="21" t="inlineStr"/>
+      <c r="I8" s="20" t="inlineStr"/>
+      <c r="J8" s="20" t="inlineStr"/>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
@@ -12174,7 +12174,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>C | 436呎 (2房)
 -
@@ -12198,7 +12198,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G9" s="20" t="inlineStr">
+      <c r="G9" s="21" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12206,7 +12206,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H9" s="20" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12214,8 +12214,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I9" s="21" t="inlineStr"/>
-      <c r="J9" s="21" t="inlineStr"/>
+      <c r="I9" s="20" t="inlineStr"/>
+      <c r="J9" s="20" t="inlineStr"/>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
@@ -12236,7 +12236,7 @@
           <t>B | 241呎 (1房)
 $720万
 $29,871/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -12263,7 +12263,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G10" s="20" t="inlineStr">
+      <c r="G10" s="21" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12271,7 +12271,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H10" s="20" t="inlineStr">
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12279,8 +12279,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I10" s="21" t="inlineStr"/>
-      <c r="J10" s="21" t="inlineStr"/>
+      <c r="I10" s="20" t="inlineStr"/>
+      <c r="J10" s="20" t="inlineStr"/>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
@@ -12328,7 +12328,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G11" s="20" t="inlineStr">
+      <c r="G11" s="21" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12336,7 +12336,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H11" s="20" t="inlineStr">
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12344,8 +12344,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I11" s="21" t="inlineStr"/>
-      <c r="J11" s="21" t="inlineStr"/>
+      <c r="I11" s="20" t="inlineStr"/>
+      <c r="J11" s="20" t="inlineStr"/>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
@@ -12393,7 +12393,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G12" s="20" t="inlineStr">
+      <c r="G12" s="21" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12401,7 +12401,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H12" s="20" t="inlineStr">
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12409,8 +12409,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I12" s="21" t="inlineStr"/>
-      <c r="J12" s="21" t="inlineStr"/>
+      <c r="I12" s="20" t="inlineStr"/>
+      <c r="J12" s="20" t="inlineStr"/>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
@@ -12431,7 +12431,7 @@
           <t>B | 241呎 (1房)
 $693万
 $28,743/呎
-(26年-06月)</t>
+(26年-06月-23日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -12466,7 +12466,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H13" s="20" t="inlineStr">
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12474,8 +12474,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I13" s="21" t="inlineStr"/>
-      <c r="J13" s="21" t="inlineStr"/>
+      <c r="I13" s="20" t="inlineStr"/>
+      <c r="J13" s="20" t="inlineStr"/>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -12488,7 +12488,7 @@
           <t>A | 388呎 (2房)
 $1037万
 $26,727/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -12520,7 +12520,7 @@
           <t>E | 255呎 (1房)
 $648万
 $25,412/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -12531,7 +12531,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H14" s="20" t="inlineStr">
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12539,8 +12539,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I14" s="21" t="inlineStr"/>
-      <c r="J14" s="21" t="inlineStr"/>
+      <c r="I14" s="20" t="inlineStr"/>
+      <c r="J14" s="20" t="inlineStr"/>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
@@ -12561,7 +12561,7 @@
           <t>B | 241呎 (1房)
 $675万
 $27,996/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
@@ -12585,7 +12585,7 @@
           <t>E | 255呎 (1房)
 $626万
 $24,549/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -12604,8 +12604,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I15" s="21" t="inlineStr"/>
-      <c r="J15" s="21" t="inlineStr"/>
+      <c r="I15" s="20" t="inlineStr"/>
+      <c r="J15" s="20" t="inlineStr"/>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
@@ -12618,7 +12618,7 @@
           <t>A | 388呎 (2房)
 $970万
 $25,000/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="C16" s="24" t="inlineStr">
@@ -12626,7 +12626,7 @@
           <t>B | 241呎 (1房)
 $653万
 $27,108/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="D16" s="24" t="inlineStr">
@@ -12634,7 +12634,7 @@
           <t>C | 436呎 (2房)
 $1155万
 $26,495/呎
-(26年-07月)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="E16" s="24" t="inlineStr">
@@ -12642,7 +12642,7 @@
           <t>D | 270呎 (1房)
 $676万
 $25,026/呎
-(26年-07月)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="F16" s="24" t="inlineStr">
@@ -12650,7 +12650,7 @@
           <t>E | 255呎 (1房)
 $621万
 $24,349/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="G16" s="23" t="inlineStr">
@@ -12669,8 +12669,8 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I16" s="21" t="inlineStr"/>
-      <c r="J16" s="21" t="inlineStr"/>
+      <c r="I16" s="20" t="inlineStr"/>
+      <c r="J16" s="20" t="inlineStr"/>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="19" t="inlineStr">
@@ -12683,7 +12683,7 @@
           <t>A | 388呎 (2房)
 $954万
 $24,601/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="C17" s="24" t="inlineStr">
@@ -12691,7 +12691,7 @@
           <t>B | 241呎 (1房)
 $652万
 $27,037/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="D17" s="24" t="inlineStr">
@@ -12699,7 +12699,7 @@
           <t>C | 436呎 (2房)
 $1085万
 $24,894/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="E17" s="24" t="inlineStr">
@@ -12707,7 +12707,7 @@
           <t>D | 270呎 (1房)
 $641万
 $23,733/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="F17" s="24" t="inlineStr">
@@ -12715,7 +12715,7 @@
           <t>E | 255呎 (1房)
 $610万
 $23,922/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -12734,8 +12734,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I17" s="21" t="inlineStr"/>
-      <c r="J17" s="21" t="inlineStr"/>
+      <c r="I17" s="20" t="inlineStr"/>
+      <c r="J17" s="20" t="inlineStr"/>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
@@ -12748,7 +12748,7 @@
           <t>A | 388呎 (2房)
 $974万
 $25,103/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="C18" s="24" t="inlineStr">
@@ -12756,7 +12756,7 @@
           <t>B | 241呎 (1房)
 $638万
 $26,490/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
@@ -12780,7 +12780,7 @@
           <t>E | 255呎 (1房)
 $611万
 $23,949/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -12799,8 +12799,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I18" s="21" t="inlineStr"/>
-      <c r="J18" s="21" t="inlineStr"/>
+      <c r="I18" s="20" t="inlineStr"/>
+      <c r="J18" s="20" t="inlineStr"/>
     </row>
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="19" t="inlineStr">
@@ -12813,7 +12813,7 @@
           <t>A | 388呎 (2房)
 $904万
 $23,299/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="C19" s="24" t="inlineStr">
@@ -12821,7 +12821,7 @@
           <t>B | 241呎 (1房)
 $628万
 $26,071/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="D19" s="24" t="inlineStr">
@@ -12829,7 +12829,7 @@
           <t>C | 436呎 (2房)
 $1016万
 $23,300/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="E19" s="23" t="inlineStr">
@@ -12845,7 +12845,7 @@
           <t>E | 255呎 (1房)
 $606万
 $23,749/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="G19" s="23" t="inlineStr">
@@ -12864,8 +12864,8 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I19" s="21" t="inlineStr"/>
-      <c r="J19" s="21" t="inlineStr"/>
+      <c r="I19" s="20" t="inlineStr"/>
+      <c r="J19" s="20" t="inlineStr"/>
     </row>
     <row r="20" ht="58" customHeight="1">
       <c r="A20" s="19" t="inlineStr">
@@ -12886,7 +12886,7 @@
           <t>B | 241呎 (1房)
 $605万
 $25,100/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="D20" s="24" t="inlineStr">
@@ -12894,7 +12894,7 @@
           <t>C | 436呎 (2房)
 $1038万
 $23,819/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="E20" s="23" t="inlineStr">
@@ -12905,7 +12905,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F20" s="20" t="inlineStr">
+      <c r="F20" s="21" t="inlineStr">
         <is>
           <t>E | 296呎 (1房)
 -
@@ -12913,7 +12913,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G20" s="20" t="inlineStr">
+      <c r="G20" s="21" t="inlineStr">
         <is>
           <t>F | 346呎 (2房)
 -
@@ -12929,8 +12929,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I20" s="21" t="inlineStr"/>
-      <c r="J20" s="21" t="inlineStr"/>
+      <c r="I20" s="20" t="inlineStr"/>
+      <c r="J20" s="20" t="inlineStr"/>
     </row>
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="19" t="inlineStr">
@@ -12943,7 +12943,7 @@
           <t>A | 389呎 (2房)
 $922万
 $23,715/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="C21" s="24" t="inlineStr">
@@ -12951,7 +12951,7 @@
           <t>B | 241呎 (1房)
 $598万
 $24,801/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="D21" s="23" t="inlineStr">
@@ -12975,7 +12975,7 @@
           <t>E | 276呎 (1房)
 $639万
 $23,149/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="G21" s="24" t="inlineStr">
@@ -12983,7 +12983,7 @@
           <t>F | 288呎 (1房)
 $687万
 $23,868/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="H21" s="24" t="inlineStr">
@@ -12991,7 +12991,7 @@
           <t>G | 277呎 (1房)
 $661万
 $23,870/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="I21" s="23" t="inlineStr">
@@ -13022,7 +13022,7 @@
           <t>A | 389呎 (2房)
 $889万
 $22,851/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="C22" s="24" t="inlineStr">
@@ -13030,7 +13030,7 @@
           <t>B | 241呎 (1房)
 $585万
 $24,261/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="D22" s="24" t="inlineStr">
@@ -13038,7 +13038,7 @@
           <t>C | 438呎 (2房)
 $994万
 $22,701/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="E22" s="24" t="inlineStr">
@@ -13046,7 +13046,7 @@
           <t>D | 271呎 (1房)
 $616万
 $22,742/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="F22" s="24" t="inlineStr">
@@ -13054,7 +13054,7 @@
           <t>E | 276呎 (1房)
 $631万
 $22,851/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="G22" s="24" t="inlineStr">
@@ -13062,7 +13062,7 @@
           <t>F | 288呎 (1房)
 $654万
 $22,698/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="H22" s="24" t="inlineStr">
@@ -13070,7 +13070,7 @@
           <t>G | 277呎 (1房)
 $633万
 $22,848/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="I22" s="23" t="inlineStr">
@@ -13101,7 +13101,7 @@
           <t>A | 389呎 (2房)
 $881万
 $22,650/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="C23" s="24" t="inlineStr">
@@ -13109,7 +13109,7 @@
           <t>B | 241呎 (1房)
 $583万
 $24,199/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
@@ -13125,7 +13125,7 @@
           <t>D | 271呎 (1房)
 $604万
 $22,299/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="F23" s="24" t="inlineStr">
@@ -13133,7 +13133,7 @@
           <t>E | 276呎 (1房)
 $640万
 $23,181/呎
-(26年-07月)</t>
+(26年-07月-05日)</t>
         </is>
       </c>
       <c r="G23" s="24" t="inlineStr">
@@ -13141,7 +13141,7 @@
           <t>F | 288呎 (1房)
 $646万
 $22,448/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="H23" s="24" t="inlineStr">
@@ -13149,7 +13149,7 @@
           <t>G | 277呎 (1房)
 $644万
 $23,249/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="I23" s="23" t="inlineStr">
@@ -13180,7 +13180,7 @@
           <t>A | 389呎 (2房)
 $873万
 $22,450/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="C24" s="24" t="inlineStr">
@@ -13188,7 +13188,7 @@
           <t>B | 241呎 (1房)
 $576万
 $23,900/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="D24" s="24" t="inlineStr">
@@ -13196,7 +13196,7 @@
           <t>C | 438呎 (2房)
 $981万
 $22,400/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="E24" s="24" t="inlineStr">
@@ -13204,7 +13204,7 @@
           <t>D | 271呎 (1房)
 $572万
 $21,114/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="F24" s="24" t="inlineStr">
@@ -13212,7 +13212,7 @@
           <t>E | 276呎 (1房)
 $608万
 $22,040/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="G24" s="24" t="inlineStr">
@@ -13220,7 +13220,7 @@
           <t>F | 288呎 (1房)
 $665万
 $23,097/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="H24" s="24" t="inlineStr">
@@ -13228,7 +13228,7 @@
           <t>G | 277呎 (1房)
 $616万
 $22,249/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="I24" s="23" t="inlineStr">
@@ -13267,7 +13267,7 @@
           <t>B | 241呎 (1房)
 $569万
 $23,602/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="D25" s="23" t="inlineStr">
@@ -13283,7 +13283,7 @@
           <t>D | 271呎 (1房)
 $564万
 $20,812/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="F25" s="23" t="inlineStr">
@@ -13299,7 +13299,7 @@
           <t>F | 288呎 (1房)
 $662万
 $22,976/呎
-(26年-06月)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="H25" s="24" t="inlineStr">
@@ -13307,7 +13307,7 @@
           <t>G | 277呎 (1房)
 $621万
 $22,422/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="I25" s="23" t="inlineStr">
@@ -13338,7 +13338,7 @@
           <t>A | 389呎 (2房)
 $884万
 $22,735/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="C26" s="24" t="inlineStr">
@@ -13346,7 +13346,7 @@
           <t>B | 241呎 (1房)
 $571万
 $23,701/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="D26" s="23" t="inlineStr">
@@ -13362,7 +13362,7 @@
           <t>D | 271呎 (1房)
 $573万
 $21,159/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="F26" s="24" t="inlineStr">
@@ -13370,7 +13370,7 @@
           <t>E | 276呎 (1房)
 $614万
 $22,243/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="G26" s="24" t="inlineStr">
@@ -13378,7 +13378,7 @@
           <t>F | 288呎 (1房)
 $631万
 $21,899/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="H26" s="24" t="inlineStr">
@@ -13386,7 +13386,7 @@
           <t>G | 277呎 (1房)
 $618万
 $22,325/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="I26" s="23" t="inlineStr">
@@ -13425,7 +13425,7 @@
           <t>B | 241呎 (1房)
 $571万
 $23,705/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="D27" s="23" t="inlineStr">
@@ -13441,7 +13441,7 @@
           <t>D | 271呎 (1房)
 $556万
 $20,506/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="F27" s="23" t="inlineStr">
@@ -13457,7 +13457,7 @@
           <t>F | 288呎 (1房)
 $624万
 $21,649/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="H27" s="24" t="inlineStr">
@@ -13465,7 +13465,7 @@
           <t>G | 277呎 (1房)
 $586万
 $21,141/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="I27" s="23" t="inlineStr">
@@ -13491,7 +13491,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B28" s="20" t="inlineStr">
+      <c r="B28" s="21" t="inlineStr">
         <is>
           <t>A | 350呎 (2房)
 -
@@ -13499,7 +13499,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C28" s="20" t="inlineStr">
+      <c r="C28" s="21" t="inlineStr">
         <is>
           <t>B | 204呎 (1房)
 -
@@ -13507,7 +13507,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D28" s="20" t="inlineStr">
+      <c r="D28" s="21" t="inlineStr">
         <is>
           <t>C | 401呎 (2房)
 -
@@ -13515,7 +13515,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E28" s="20" t="inlineStr">
+      <c r="E28" s="21" t="inlineStr">
         <is>
           <t>D | 234呎 (1房)
 -
@@ -13523,7 +13523,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F28" s="20" t="inlineStr">
+      <c r="F28" s="21" t="inlineStr">
         <is>
           <t>E | 238呎 (1房)
 -
@@ -13531,7 +13531,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G28" s="20" t="inlineStr">
+      <c r="G28" s="21" t="inlineStr">
         <is>
           <t>F | 250呎 (1房)
 -
@@ -13539,7 +13539,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H28" s="20" t="inlineStr">
+      <c r="H28" s="21" t="inlineStr">
         <is>
           <t>G | 240呎 (1房)
 -
@@ -13547,7 +13547,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I28" s="20" t="inlineStr">
+      <c r="I28" s="21" t="inlineStr">
         <is>
           <t>H | 192呎 (开放式)
 -
@@ -13555,7 +13555,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J28" s="20" t="inlineStr">
+      <c r="J28" s="21" t="inlineStr">
         <is>
           <t>J | 199呎 (开放式)
 -
